--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757903DA-720C-497D-8AC6-6015072AF20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D364A3B-E123-489B-89E2-4BBABB627D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="228">
   <si>
     <t>이름</t>
   </si>
@@ -194,9 +194,6 @@
     <t>10 totes</t>
   </si>
   <si>
-    <t>7 PLT</t>
-  </si>
-  <si>
     <t>8 PLT</t>
   </si>
   <si>
@@ -215,12 +212,6 @@
     <t>1 PLT</t>
   </si>
   <si>
-    <t>1.8 FTL</t>
-  </si>
-  <si>
-    <t>10 PLT</t>
-  </si>
-  <si>
     <t>15 PLT</t>
   </si>
   <si>
@@ -729,6 +720,12 @@
   </si>
   <si>
     <t>8/21 휴가 예정</t>
+  </si>
+  <si>
+    <t>3 FTL</t>
+  </si>
+  <si>
+    <t>1.2 FTL</t>
   </si>
 </sst>
 </file>
@@ -1213,7 +1210,7 @@
     </row>
     <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
@@ -1225,12 +1222,12 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -1245,7 +1242,7 @@
     </row>
     <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -1260,19 +1257,19 @@
     </row>
     <row r="6" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -1312,7 +1309,7 @@
         <v>7</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>9</v>
@@ -1332,16 +1329,16 @@
         <v>27</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>42</v>
+        <v>226</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>42</v>
+        <v>226</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I3" s="6">
         <v>46244</v>
@@ -1364,10 +1361,10 @@
         <v>49</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I4" s="6">
         <v>46254</v>
@@ -1387,13 +1384,13 @@
         <v>50</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I5" s="6">
         <v>46258</v>
@@ -1410,16 +1407,16 @@
         <v>32</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="G6" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I6" s="6">
         <v>46254</v>
@@ -1436,16 +1433,16 @@
         <v>32</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="G7" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I7" s="6">
         <v>46254</v>
@@ -1465,10 +1462,10 @@
         <v>54</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>46</v>
@@ -1488,13 +1485,13 @@
         <v>44</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>46</v>
@@ -1514,16 +1511,16 @@
         <v>29</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I10" s="6">
         <v>46258</v>
@@ -1540,16 +1537,16 @@
         <v>38</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>57</v>
+        <v>227</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>42</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I11" s="6">
         <v>46260</v>
@@ -1566,13 +1563,13 @@
         <v>40</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>47</v>
@@ -1592,13 +1589,13 @@
         <v>41</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H13" s="6">
         <v>46262</v>
@@ -1646,10 +1643,10 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E3" s="3">
         <v>46217</v>
@@ -1661,16 +1658,16 @@
         <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E4" s="3">
         <v>46218</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1678,16 +1675,16 @@
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E5" s="3">
         <v>46223</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1695,16 +1692,16 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E6" s="3">
         <v>46225</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1712,16 +1709,16 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E7" s="3">
         <v>46226</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1729,10 +1726,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E8" s="3">
         <v>46232</v>
@@ -1744,16 +1741,16 @@
         <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E9" s="3">
         <v>46234</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1761,16 +1758,16 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E10" s="3">
         <v>46237</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1778,10 +1775,10 @@
         <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="3">
         <v>46223</v>
@@ -1793,10 +1790,10 @@
         <v>19</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="3">
         <v>46223</v>
@@ -1808,16 +1805,16 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E13" s="3">
         <v>46238</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1825,10 +1822,10 @@
         <v>19</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3">
         <v>46239</v>
@@ -1840,10 +1837,10 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E15" s="3">
         <v>46241</v>
@@ -1855,16 +1852,16 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E16" s="3">
         <v>46244</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1872,16 +1869,16 @@
         <v>19</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E17" s="3">
         <v>46251</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1889,16 +1886,16 @@
         <v>19</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E18" s="3">
         <v>46251</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1906,10 +1903,10 @@
         <v>19</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E19" s="3">
         <v>46253</v>
@@ -1921,16 +1918,16 @@
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E20" s="3">
         <v>46258</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1938,10 +1935,10 @@
         <v>19</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" s="3">
         <v>46251</v>
@@ -1953,10 +1950,10 @@
         <v>19</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E22" s="3">
         <v>46261</v>
@@ -2049,18 +2046,18 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C3" s="8">
         <v>4.13</v>
@@ -2069,7 +2066,7 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C4" s="8">
         <v>4.1099999999999994</v>
@@ -2078,7 +2075,7 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C5" s="8">
         <v>4.1999999999999993</v>
@@ -2089,7 +2086,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C6" s="8">
         <v>4.2199999999999989</v>
@@ -2098,7 +2095,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C7" s="8">
         <v>4.1599999999999993</v>
@@ -2107,7 +2104,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C8" s="8">
         <v>4.2399999999999993</v>
@@ -2116,7 +2113,7 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C9" s="8">
         <v>4.2799999999999994</v>
@@ -2125,7 +2122,7 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C10" s="8">
         <v>4.2399999999999993</v>
@@ -2136,7 +2133,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C11" s="8">
         <v>4.1999999999999993</v>
@@ -2145,7 +2142,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C12" s="8">
         <v>4.2299999999999995</v>
@@ -2156,7 +2153,7 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C13" s="8">
         <v>4.1599999999999993</v>
@@ -2165,7 +2162,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C14" s="8">
         <v>4.3099999999999996</v>
@@ -2174,7 +2171,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C15" s="8">
         <v>4.2399999999999993</v>
@@ -2185,7 +2182,7 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C16" s="8">
         <v>4.2799999999999994</v>
@@ -2194,7 +2191,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C17" s="8">
         <v>4.3299999999999992</v>
@@ -2203,7 +2200,7 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C18" s="8">
         <v>4.339999999999999</v>
@@ -2212,7 +2209,7 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C19" s="8">
         <v>4.3299999999999992</v>
@@ -2221,7 +2218,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C20" s="8">
         <v>4.2399999999999993</v>
@@ -2230,7 +2227,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C21" s="8">
         <v>4.2199999999999989</v>
@@ -2239,7 +2236,7 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C22" s="8">
         <v>4.2199999999999989</v>
@@ -2248,7 +2245,7 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C23" s="8">
         <v>4.2799999999999994</v>
@@ -2257,7 +2254,7 @@
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C24" s="8">
         <v>4.3299999999999992</v>
@@ -2268,7 +2265,7 @@
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C25" s="8">
         <v>4.3099999999999996</v>
@@ -2277,7 +2274,7 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C26" s="8">
         <v>4.2499999999999991</v>
@@ -2288,7 +2285,7 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C27" s="8">
         <v>4.2699999999999996</v>
@@ -2297,7 +2294,7 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C28" s="8">
         <v>4.2699999999999996</v>
@@ -2308,7 +2305,7 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C29" s="8">
         <v>4.3099999999999996</v>
@@ -2317,7 +2314,7 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C30" s="8">
         <v>4.2299999999999995</v>
@@ -2328,7 +2325,7 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C31" s="8">
         <v>4.2299999999999995</v>
@@ -2337,7 +2334,7 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C32" s="8">
         <v>4.18</v>
@@ -2348,7 +2345,7 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C33" s="8">
         <v>4.2599999999999989</v>
@@ -2357,7 +2354,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C34" s="8">
         <v>4.2699999999999996</v>
@@ -2366,7 +2363,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C35" s="8">
         <v>4.2599999999999989</v>
@@ -2375,7 +2372,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C36" s="8">
         <v>4.2399999999999993</v>
@@ -2386,7 +2383,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C37" s="8">
         <v>4.2899999999999991</v>
@@ -2395,7 +2392,7 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C38" s="8">
         <v>4.2899999999999991</v>
@@ -2404,7 +2401,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C39" s="8">
         <v>4.3099999999999996</v>
@@ -2413,7 +2410,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C40" s="8">
         <v>4.3899999999999997</v>
@@ -2424,7 +2421,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C41" s="8">
         <v>4.4099999999999993</v>
@@ -2433,7 +2430,7 @@
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C42" s="8">
         <v>4.419999999999999</v>
@@ -2444,7 +2441,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C43" s="8">
         <v>4.4499999999999993</v>
@@ -2453,7 +2450,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C44" s="8">
         <v>4.4699999999999989</v>
@@ -2462,7 +2459,7 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C45" s="8">
         <v>4.4799999999999995</v>
@@ -2471,7 +2468,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C46" s="8">
         <v>4.4899999999999993</v>
@@ -2480,7 +2477,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C47" s="8">
         <v>4.669999999999999</v>
@@ -2491,7 +2488,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C48" s="8">
         <v>4.5799999999999992</v>
@@ -2500,7 +2497,7 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C49" s="8">
         <v>4.669999999999999</v>
@@ -2509,7 +2506,7 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C50" s="8">
         <v>4.5699999999999994</v>
@@ -2520,7 +2517,7 @@
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C51" s="8">
         <v>4.589999999999999</v>
@@ -2529,7 +2526,7 @@
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C52" s="8">
         <v>4.5499999999999989</v>
@@ -2540,7 +2537,7 @@
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C53" s="8">
         <v>4.7199999999999989</v>
@@ -2549,7 +2546,7 @@
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C54" s="8">
         <v>4.6399999999999997</v>
@@ -2558,7 +2555,7 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C55" s="8">
         <v>4.6499999999999995</v>
@@ -2569,7 +2566,7 @@
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C56" s="8">
         <v>4.6399999999999997</v>
@@ -2578,7 +2575,7 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C57" s="8">
         <v>4.6099999999999994</v>
@@ -2589,7 +2586,7 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C58" s="8">
         <v>4.5299999999999994</v>
@@ -2600,7 +2597,7 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C59" s="8">
         <v>4.6599999999999993</v>
@@ -2609,7 +2606,7 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C60" s="8">
         <v>4.4999999999999991</v>
@@ -2618,7 +2615,7 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C61" s="8">
         <v>4.5599999999999996</v>
@@ -2627,7 +2624,7 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C62" s="8">
         <v>4.5299999999999994</v>
@@ -2638,7 +2635,7 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C63" s="8">
         <v>4.5099999999999989</v>
@@ -2647,7 +2644,7 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C64" s="8">
         <v>4.5499999999999989</v>
@@ -2656,7 +2653,7 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C65" s="8">
         <v>4.5099999999999989</v>
@@ -2665,7 +2662,7 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C66" s="8">
         <v>4.4599999999999991</v>
@@ -2674,7 +2671,7 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C67" s="8">
         <v>4.4499999999999993</v>
@@ -2683,7 +2680,7 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C68" s="8">
         <v>4.4499999999999993</v>
@@ -2694,7 +2691,7 @@
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C69" s="8">
         <v>4.3999999999999995</v>
@@ -2703,7 +2700,7 @@
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C70" s="8">
         <v>4.3599999999999994</v>
@@ -2712,7 +2709,7 @@
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C71" s="8">
         <v>4.3599999999999994</v>
@@ -2723,7 +2720,7 @@
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C72" s="8">
         <v>4.2599999999999989</v>
@@ -2732,7 +2729,7 @@
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C73" s="8">
         <v>4.2299999999999995</v>
@@ -2743,7 +2740,7 @@
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C74" s="8">
         <v>4.2499999999999991</v>
@@ -2752,7 +2749,7 @@
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C75" s="8">
         <v>4.2199999999999989</v>
@@ -2761,7 +2758,7 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C76" s="8">
         <v>4.2499999999999991</v>
@@ -2772,7 +2769,7 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C77" s="8">
         <v>4.2599999999999989</v>
@@ -2781,7 +2778,7 @@
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C78" s="8">
         <v>4.2699999999999996</v>
@@ -2792,7 +2789,7 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C79" s="8">
         <v>4.17</v>
@@ -2801,7 +2798,7 @@
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C80" s="8">
         <v>4.2399999999999993</v>
@@ -2810,7 +2807,7 @@
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C81" s="8">
         <v>4.2399999999999993</v>
@@ -2821,7 +2818,7 @@
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C82" s="8">
         <v>4.2499999999999991</v>
@@ -2830,7 +2827,7 @@
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C83" s="8">
         <v>4.2799999999999994</v>
@@ -2841,7 +2838,7 @@
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C84" s="8">
         <v>4.3099999999999996</v>
@@ -2850,7 +2847,7 @@
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C85" s="8">
         <v>4.2899999999999991</v>
@@ -2859,7 +2856,7 @@
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C86" s="8">
         <v>4.3199999999999994</v>
@@ -2870,7 +2867,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C87" s="8">
         <v>4.419999999999999</v>
@@ -2879,7 +2876,7 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C88" s="8">
         <v>4.3699999999999992</v>
@@ -2890,7 +2887,7 @@
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C89" s="8">
         <v>4.3699999999999992</v>
@@ -2899,7 +2896,7 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C90" s="8">
         <v>4.379999999999999</v>
@@ -2908,7 +2905,7 @@
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C91" s="8">
         <v>4.3899999999999997</v>
@@ -2917,7 +2914,7 @@
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C92" s="8">
         <v>4.43</v>
@@ -2926,7 +2923,7 @@
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C93" s="8">
         <v>4.3099999999999996</v>
@@ -2937,7 +2934,7 @@
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B94" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C94" s="8">
         <v>4.3899999999999997</v>
@@ -2946,7 +2943,7 @@
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B95" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C95" s="8">
         <v>4.4399999999999995</v>
@@ -2955,7 +2952,7 @@
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B96" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C96" s="8">
         <v>4.3999999999999995</v>
@@ -2964,7 +2961,7 @@
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C97" s="8">
         <v>4.4399999999999995</v>
@@ -2973,7 +2970,7 @@
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C98" s="8">
         <v>4.379999999999999</v>
@@ -2984,7 +2981,7 @@
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C99" s="8">
         <v>4.4599999999999991</v>
@@ -2993,7 +2990,7 @@
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C100" s="8">
         <v>4.419999999999999</v>
@@ -3002,7 +2999,7 @@
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C101" s="8">
         <v>4.5199999999999996</v>
@@ -3013,7 +3010,7 @@
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C102" s="8">
         <v>4.4399999999999995</v>
@@ -3022,7 +3019,7 @@
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C103" s="8">
         <v>4.5399999999999991</v>
@@ -3031,7 +3028,7 @@
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C104" s="8">
         <v>4.4799999999999995</v>
@@ -3040,7 +3037,7 @@
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C105" s="8">
         <v>4.5299999999999994</v>
@@ -3051,7 +3048,7 @@
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C106" s="8">
         <v>4.4899999999999993</v>
@@ -3060,7 +3057,7 @@
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C107" s="8">
         <v>4.4999999999999991</v>
@@ -3071,7 +3068,7 @@
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C108" s="8">
         <v>4.5799999999999992</v>
@@ -3080,7 +3077,7 @@
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C109" s="8">
         <v>4.5699999999999994</v>
@@ -3089,7 +3086,7 @@
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C110" s="8">
         <v>4.4699999999999989</v>
@@ -3100,7 +3097,7 @@
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C111" s="8">
         <v>4.379999999999999</v>
@@ -3109,7 +3106,7 @@
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C112" s="8">
         <v>4.589999999999999</v>
@@ -3120,7 +3117,7 @@
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C113" s="8">
         <v>4.6399999999999997</v>
@@ -3129,7 +3126,7 @@
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C114" s="8">
         <v>4.5099999999999989</v>
@@ -3138,7 +3135,7 @@
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C115" s="8">
         <v>4.5299999999999994</v>
@@ -3147,7 +3144,7 @@
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C116" s="8">
         <v>4.5599999999999996</v>
@@ -3156,7 +3153,7 @@
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C117" s="8">
         <v>4.6499999999999995</v>
@@ -3165,7 +3162,7 @@
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C118" s="8">
         <v>4.5599999999999996</v>
@@ -3174,7 +3171,7 @@
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B119" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C119" s="8">
         <v>4.6499999999999995</v>
@@ -3185,7 +3182,7 @@
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C120" s="8">
         <v>4.5999999999999996</v>
@@ -3194,7 +3191,7 @@
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B121" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C121" s="8">
         <v>4.6099999999999994</v>
@@ -3203,7 +3200,7 @@
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B122" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C122" s="8">
         <v>4.6599999999999993</v>
@@ -3212,7 +3209,7 @@
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B123" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C123" s="8">
         <v>4.5999999999999996</v>
@@ -3223,7 +3220,7 @@
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C124" s="8">
         <v>4.629999999999999</v>
@@ -3232,7 +3229,7 @@
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B125" s="7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C125" s="8">
         <v>4.6099999999999994</v>
@@ -3241,7 +3238,7 @@
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C126" s="8">
         <v>4.669999999999999</v>
@@ -3250,7 +3247,7 @@
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B127" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C127" s="8">
         <v>4.5599999999999996</v>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D364A3B-E123-489B-89E2-4BBABB627D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD5936A-AEC9-47F8-9348-30C994B25B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="3135" yWindow="2820" windowWidth="11415" windowHeight="12330" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="인사및일정" sheetId="1" r:id="rId1"/>
     <sheet name="재고현황" sheetId="2" r:id="rId2"/>
     <sheet name="운영스케줄" sheetId="3" r:id="rId3"/>
     <sheet name="소전각 가격" sheetId="4" r:id="rId4"/>
+    <sheet name="원부자재 구매액" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="243">
   <si>
     <t>이름</t>
   </si>
@@ -680,9 +681,6 @@
     <t>Weee!</t>
   </si>
   <si>
-    <t>OFF</t>
-  </si>
-  <si>
     <t>LA Changtuh</t>
   </si>
   <si>
@@ -726,6 +724,54 @@
   </si>
   <si>
     <t>1.2 FTL</t>
+  </si>
+  <si>
+    <t>2025년 전체</t>
+  </si>
+  <si>
+    <t>26년 1월</t>
+  </si>
+  <si>
+    <t>26년 2월</t>
+  </si>
+  <si>
+    <t>26년 3월</t>
+  </si>
+  <si>
+    <t>26년 4월</t>
+  </si>
+  <si>
+    <t>26년 5월</t>
+  </si>
+  <si>
+    <t>26년 6월</t>
+  </si>
+  <si>
+    <t>26년 7월</t>
+  </si>
+  <si>
+    <t>26년 8월</t>
+  </si>
+  <si>
+    <t>26년 9월</t>
+  </si>
+  <si>
+    <t>2026년 누적</t>
+  </si>
+  <si>
+    <t>2026년 월평균</t>
+  </si>
+  <si>
+    <t>2025년 월평균</t>
+  </si>
+  <si>
+    <t>26년 10월</t>
+  </si>
+  <si>
+    <t>26년 11월</t>
+  </si>
+  <si>
+    <t>26년 12월</t>
   </si>
 </sst>
 </file>
@@ -815,7 +861,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -838,6 +884,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1222,7 +1269,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -1264,7 +1311,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>212</v>
+        <v>3</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -1329,16 +1376,16 @@
         <v>27</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>201</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I3" s="6">
         <v>46244</v>
@@ -1364,7 +1411,7 @@
         <v>202</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I4" s="6">
         <v>46254</v>
@@ -1390,7 +1437,7 @@
         <v>203</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I5" s="6">
         <v>46258</v>
@@ -1416,7 +1463,7 @@
         <v>202</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I6" s="6">
         <v>46254</v>
@@ -1442,7 +1489,7 @@
         <v>202</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I7" s="6">
         <v>46254</v>
@@ -1520,7 +1567,7 @@
         <v>203</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I10" s="6">
         <v>46258</v>
@@ -1537,7 +1584,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>42</v>
@@ -1822,7 +1869,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>53</v>
@@ -1861,7 +1908,7 @@
         <v>46244</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1878,7 +1925,7 @@
         <v>46251</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1895,7 +1942,7 @@
         <v>46251</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1927,7 +1974,7 @@
         <v>46258</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1935,7 +1982,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>55</v>
@@ -1950,10 +1997,10 @@
         <v>19</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="E22" s="3">
         <v>46261</v>
@@ -3573,6 +3620,182 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1659F036-C4D7-4C7F-A46E-B20A44632319}">
+  <dimension ref="C3:E19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C4" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" s="8">
+        <v>15520853.789999999</v>
+      </c>
+      <c r="E4" s="8">
+        <v>2158325.56</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D5" s="8">
+        <f>D4/12</f>
+        <v>1293404.4824999999</v>
+      </c>
+      <c r="E5" s="8">
+        <f>E4/12</f>
+        <v>179860.46333333335</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D6" s="8">
+        <v>8817263.6600000001</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1242029.71</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" s="8">
+        <f>D6/7</f>
+        <v>1259609.0942857142</v>
+      </c>
+      <c r="E7" s="8">
+        <f>E6/7</f>
+        <v>177432.81571428571</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1325698.24</v>
+      </c>
+      <c r="E8" s="10">
+        <v>245415.15</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1188990.72</v>
+      </c>
+      <c r="E9" s="10">
+        <v>138304.81</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1614650.34</v>
+      </c>
+      <c r="E10" s="10">
+        <v>215806.1</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1403205.37</v>
+      </c>
+      <c r="E11" s="10">
+        <v>237457.48</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1183673.21</v>
+      </c>
+      <c r="E12" s="10">
+        <v>149296.85999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1289298.07</v>
+      </c>
+      <c r="E13" s="10">
+        <v>63267.48</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>234</v>
+      </c>
+      <c r="D14" s="10">
+        <v>811747.71</v>
+      </c>
+      <c r="E14" s="10">
+        <v>192481.83</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{6b89535c-2ba5-4f71-a34a-075d8392d04a}" enabled="1" method="Privileged" siteId="{d4ffc887-d88d-41cc-bf6a-6bb47ec0f3ca}" contentBits="0" removed="0"/>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD5936A-AEC9-47F8-9348-30C994B25B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8AF5B3-6598-4789-9258-555FEC27B4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="2820" windowWidth="11415" windowHeight="12330" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="16695" yWindow="1890" windowWidth="11415" windowHeight="12330" activeTab="3" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="인사및일정" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="247">
   <si>
     <t>이름</t>
   </si>
@@ -772,6 +772,18 @@
   </si>
   <si>
     <t>26년 12월</t>
+  </si>
+  <si>
+    <t>시장가격 누계 평균</t>
+  </si>
+  <si>
+    <t>구매가격 누계평균</t>
+  </si>
+  <si>
+    <t>차이</t>
+  </si>
+  <si>
+    <t>누계 구매량</t>
   </si>
 </sst>
 </file>
@@ -857,11 +869,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -885,10 +898,23 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2084,14 +2110,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8B69F2-ABF3-479B-9A70-167875A2ADD6}">
-  <dimension ref="B2:F155"/>
+  <dimension ref="B2:H155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>184</v>
       </c>
@@ -2102,7 +2131,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>60</v>
       </c>
@@ -2110,8 +2139,14 @@
         <v>4.13</v>
       </c>
       <c r="D3" s="8"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="G3" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="H3" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>61</v>
       </c>
@@ -2119,8 +2154,15 @@
         <v>4.1099999999999994</v>
       </c>
       <c r="D4" s="8"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="G4" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="H4" s="12">
+        <f>AVERAGE(D3:D155)</f>
+        <v>4.3290244121951229</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>62</v>
       </c>
@@ -2130,8 +2172,15 @@
       <c r="D5" s="8">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="G5" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="H5" s="13">
+        <f>(H4-H3)/H3</f>
+        <v>-1.6130815410199419E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>63</v>
       </c>
@@ -2139,8 +2188,15 @@
         <v>4.2199999999999989</v>
       </c>
       <c r="D6" s="8"/>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="G6" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="H6" s="11" t="str">
+        <f>COUNT(D3:D370)&amp;"FTL"</f>
+        <v>41FTL</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>64</v>
       </c>
@@ -2149,7 +2205,7 @@
       </c>
       <c r="D7" s="8"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>65</v>
       </c>
@@ -2158,7 +2214,7 @@
       </c>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>66</v>
       </c>
@@ -2167,7 +2223,7 @@
       </c>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>67</v>
       </c>
@@ -2178,7 +2234,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>68</v>
       </c>
@@ -2187,7 +2243,7 @@
       </c>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>69</v>
       </c>
@@ -2198,7 +2254,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
         <v>70</v>
       </c>
@@ -2207,7 +2263,7 @@
       </c>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
         <v>71</v>
       </c>
@@ -2216,7 +2272,7 @@
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
         <v>72</v>
       </c>
@@ -2227,7 +2283,7 @@
         <v>4.2299999000000001</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
         <v>73</v>
       </c>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8AF5B3-6598-4789-9258-555FEC27B4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C217C5F6-8180-44C5-BFF3-55B019924A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16695" yWindow="1890" windowWidth="11415" windowHeight="12330" activeTab="3" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="16695" yWindow="1890" windowWidth="11415" windowHeight="12330" firstSheet="1" activeTab="2" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="인사및일정" sheetId="1" r:id="rId1"/>
@@ -1931,7 +1931,7 @@
         <v>187</v>
       </c>
       <c r="E16" s="3">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>213</v>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C217C5F6-8180-44C5-BFF3-55B019924A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E565AA8E-565E-45A2-ACF3-F166F85F9BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16695" yWindow="1890" windowWidth="11415" windowHeight="12330" firstSheet="1" activeTab="2" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="14250" yWindow="615" windowWidth="11415" windowHeight="12330" firstSheet="4" activeTab="5" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="인사및일정" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="운영스케줄" sheetId="3" r:id="rId3"/>
     <sheet name="소전각 가격" sheetId="4" r:id="rId4"/>
     <sheet name="원부자재 구매액" sheetId="5" r:id="rId5"/>
+    <sheet name="월별 재고 요약" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="363">
   <si>
     <t>이름</t>
   </si>
@@ -784,16 +785,367 @@
   </si>
   <si>
     <t>누계 구매량</t>
+  </si>
+  <si>
+    <t>283차 - 외부창고</t>
+  </si>
+  <si>
+    <t>Kroger</t>
+  </si>
+  <si>
+    <t>발주
+가능</t>
+  </si>
+  <si>
+    <t>PK 차돌박이된장찌개(prop65)</t>
+  </si>
+  <si>
+    <t>PK 육개장</t>
+  </si>
+  <si>
+    <t>PK 부대찌개(prop65)</t>
+  </si>
+  <si>
+    <t>PK 설렁탕</t>
+  </si>
+  <si>
+    <t>PK 소고기 미역국</t>
+  </si>
+  <si>
+    <t>PK 김치찌개(prop65)</t>
+  </si>
+  <si>
+    <t>PK 김치제육볶음</t>
+  </si>
+  <si>
+    <t>PK 시래기 감자탕</t>
+  </si>
+  <si>
+    <t>PK 불맛 짬뽕탕(prop65)</t>
+  </si>
+  <si>
+    <t>PK 불맛짜장</t>
+  </si>
+  <si>
+    <t>PK 뚝배기 버섯 불고기</t>
+  </si>
+  <si>
+    <t>PK 진한 사골육수</t>
+  </si>
+  <si>
+    <t>PK 안동식 찜닭</t>
+  </si>
+  <si>
+    <t>PK 닭볶음탕</t>
+  </si>
+  <si>
+    <t>PK 춘천식 닭갈비</t>
+  </si>
+  <si>
+    <t>PK 갈비탕</t>
+  </si>
+  <si>
+    <t>PK 얼큰 대파 갈비탕</t>
+  </si>
+  <si>
+    <t>Walmart 미역국</t>
+  </si>
+  <si>
+    <t>Walmart 설렁탕</t>
+  </si>
+  <si>
+    <t>Walmart 김치찌개</t>
+  </si>
+  <si>
+    <t>Walmart 육개장</t>
+  </si>
+  <si>
+    <t>PK 차돌박이 육개장 (상온)</t>
+  </si>
+  <si>
+    <t>PK 치즈부대찌개 (상온)</t>
+  </si>
+  <si>
+    <t>PK 순두부 찌개 (상온)</t>
+  </si>
+  <si>
+    <t>PK 설렁탕 (상온)</t>
+  </si>
+  <si>
+    <t>PK 강된장 (상온)</t>
+  </si>
+  <si>
+    <t>농심 부대찌개 Base</t>
+  </si>
+  <si>
+    <t>BULK Beef Bulgogi (Metro)</t>
+  </si>
+  <si>
+    <t>Bulk Beef Bulgogi(NW)</t>
+  </si>
+  <si>
+    <t>BULK LA갈비(Metro)</t>
+  </si>
+  <si>
+    <t>Costco 육개장</t>
+  </si>
+  <si>
+    <t>Costco 마파두부</t>
+  </si>
+  <si>
+    <t>Costco 소미역국</t>
+  </si>
+  <si>
+    <t>한상 김치찌개</t>
+  </si>
+  <si>
+    <t>한상 된장찌개</t>
+  </si>
+  <si>
+    <t>한상 따로국밥</t>
+  </si>
+  <si>
+    <t>한상 사골농축액</t>
+  </si>
+  <si>
+    <t>한상 설렁탕</t>
+  </si>
+  <si>
+    <t>한상 육개장</t>
+  </si>
+  <si>
+    <t>한상 부대찌개</t>
+  </si>
+  <si>
+    <t>한상 버섯불고기</t>
+  </si>
+  <si>
+    <t>한상 돼지 감자탕</t>
+  </si>
+  <si>
+    <t>한상 닭곰탕</t>
+  </si>
+  <si>
+    <t>한상 황태해장국 (Pro65)</t>
+  </si>
+  <si>
+    <t>한상 시래기 갈비탕</t>
+  </si>
+  <si>
+    <t>한상 들깨 미역국</t>
+  </si>
+  <si>
+    <t>PK 소불고기 (영문)</t>
+  </si>
+  <si>
+    <t>PK 돼지불고기 (영문)</t>
+  </si>
+  <si>
+    <t>PK 닭불고기 (영문)</t>
+  </si>
+  <si>
+    <t>PK LA갈비 (영문)</t>
+  </si>
+  <si>
+    <t>PK 고추장삼겹 (영문)</t>
+  </si>
+  <si>
+    <t>PK 붉닭구이 (영문)</t>
+  </si>
+  <si>
+    <t>PK 허니갈릭치킨 (영문)</t>
+  </si>
+  <si>
+    <t>WM 소불고기</t>
+  </si>
+  <si>
+    <t>WM 소갈비</t>
+  </si>
+  <si>
+    <t>Hmart 8 oz 소불고기</t>
+  </si>
+  <si>
+    <t>Hmart 16 oz 소불고기</t>
+  </si>
+  <si>
+    <t>Kroger 소불고기</t>
+  </si>
+  <si>
+    <t>PK 소불고기 (국문)</t>
+  </si>
+  <si>
+    <t>PK 돼지불고기 (국문)</t>
+  </si>
+  <si>
+    <t>PK 닭불고기 (국문)</t>
+  </si>
+  <si>
+    <t>PK LA갈비 (국문)</t>
+  </si>
+  <si>
+    <t>PK 고추장삼겹 (국문)</t>
+  </si>
+  <si>
+    <t>PK 붉닭구이 (국문)</t>
+  </si>
+  <si>
+    <t>한상 소불고기 (국문)</t>
+  </si>
+  <si>
+    <t>한상 돼지불고기 (국문)</t>
+  </si>
+  <si>
+    <t>한상 닭불고기 (국문)</t>
+  </si>
+  <si>
+    <t>한상 LA갈비 (국문)</t>
+  </si>
+  <si>
+    <t>한상 고추장삼겹 (국문)</t>
+  </si>
+  <si>
+    <t>한상 붉닭구이 (국문)</t>
+  </si>
+  <si>
+    <t>Kroger 소불고기 (6개입,영문)</t>
+  </si>
+  <si>
+    <t>Kroger 돼지불고기 (6개입, 영문)</t>
+  </si>
+  <si>
+    <t>Kroger 닭불고기 (6개입, 영문)</t>
+  </si>
+  <si>
+    <t>Kroger LA갈비 (6개입, 영문)</t>
+  </si>
+  <si>
+    <t>Kroger 고추장삼겹 (6개입, 영문)</t>
+  </si>
+  <si>
+    <t>Kroger 붉닭구이 (6개입, 영문)</t>
+  </si>
+  <si>
+    <t>TJ's 소불고기</t>
+  </si>
+  <si>
+    <t>Costco 소불고기(임시)</t>
+  </si>
+  <si>
+    <t>Costco LA갈비(임시)</t>
+  </si>
+  <si>
+    <t>Costco 닭불고기(임시)</t>
+  </si>
+  <si>
+    <t>Costco 고추장 삼겹살(임시)</t>
+  </si>
+  <si>
+    <t>한상 소고기 미역국(수출용)</t>
+  </si>
+  <si>
+    <t>한상 설렁탕(수출용)</t>
+  </si>
+  <si>
+    <t>한상 육개장(수출용)</t>
+  </si>
+  <si>
+    <t>PK 애호박돼지찌개</t>
+  </si>
+  <si>
+    <t>PK 닭개장</t>
+  </si>
+  <si>
+    <t>PK 소고기 달걀 장조림</t>
+  </si>
+  <si>
+    <t>PK 인도식 치킨 커리</t>
+  </si>
+  <si>
+    <t>PK 태국 치킨 레드 커리</t>
+  </si>
+  <si>
+    <t>김치 살사 (Metro)</t>
+  </si>
+  <si>
+    <t>태국 치킨 레드 커리 (Metro)</t>
+  </si>
+  <si>
+    <t>PK Kimchi Tomatoa Salsa w/ Bacon</t>
+  </si>
+  <si>
+    <t>PK Bulgogi Cream Pasta Sauce</t>
+  </si>
+  <si>
+    <t>PK Beef Bulgogi</t>
+  </si>
+  <si>
+    <t>PK Cajun Chicken</t>
+  </si>
+  <si>
+    <t>PK Spicy Pork Belly</t>
+  </si>
+  <si>
+    <t>BULK Pulled Pork (Metro)</t>
+  </si>
+  <si>
+    <t>PK 주꾸미 삼겹살</t>
+  </si>
+  <si>
+    <t>PK 홍합미역국</t>
+  </si>
+  <si>
+    <t>박스</t>
+  </si>
+  <si>
+    <t>팔렛</t>
+  </si>
+  <si>
+    <t>PK 국탕류 재고</t>
+  </si>
+  <si>
+    <t>한상 국탕류 재고</t>
+  </si>
+  <si>
+    <t>Kroger 소불고기 재고</t>
+  </si>
+  <si>
+    <t>TJ 소불고기 재고</t>
+  </si>
+  <si>
+    <t>국탕류 100개 미만 품목</t>
+  </si>
+  <si>
+    <t>국탕류 300개 이상 품목</t>
+  </si>
+  <si>
+    <t>특이사항</t>
+  </si>
+  <si>
+    <t>공장</t>
+  </si>
+  <si>
+    <t>외부창고</t>
+  </si>
+  <si>
+    <t>건</t>
+  </si>
+  <si>
+    <t>PK 및 기타 가열육 재고</t>
+  </si>
+  <si>
+    <t>재고 현황 요약</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -820,6 +1172,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -869,12 +1234,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -907,11 +1273,49 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
@@ -2034,17 +2438,35 @@
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="3">
+        <v>46252</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="24" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="3"/>
+      <c r="B24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="3">
+        <v>46245</v>
+      </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2188,7 +2610,7 @@
         <v>4.2199999999999989</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="11" t="s">
         <v>246</v>
       </c>
       <c r="H6" s="11" t="str">
@@ -3852,6 +4274,960 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F11735F-D076-4A2C-9627-3496A0571C22}">
+  <dimension ref="B2:J103"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5" s="16">
+        <v>275</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="F5" s="25">
+        <f>SUM(C5:C35)</f>
+        <v>4138</v>
+      </c>
+      <c r="G5" s="25">
+        <f>SUM(C5:C21)/72+C35/45</f>
+        <v>61.322222222222223</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="I5" s="7">
+        <f>COUNTIF(C5:C15,"&lt;100")+COUNTIF(C20:C21,"&lt;100")</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" s="16">
+        <v>248</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="I6" s="7">
+        <f>COUNTIF(C5:C15,"&gt;300")+COUNTIF(C20:C21,"&gt;300")</f>
+        <v>4</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" s="16">
+        <v>370</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="F7" s="20">
+        <v>0</v>
+      </c>
+      <c r="G7" s="21">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="16">
+        <v>258</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="F8" s="20">
+        <f>SUM(C49:C56)</f>
+        <v>429</v>
+      </c>
+      <c r="G8" s="21">
+        <f>F8/84</f>
+        <v>5.1071428571428568</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="C9" s="16">
+        <v>283</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="F9" s="22">
+        <f>C62</f>
+        <v>2590</v>
+      </c>
+      <c r="G9" s="21">
+        <f>F9/84</f>
+        <v>30.833333333333332</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="C10" s="16">
+        <v>318</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="F10" s="26">
+        <f>C81</f>
+        <v>4076</v>
+      </c>
+      <c r="G10" s="27">
+        <f>F10/42</f>
+        <v>97.047619047619051</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="I10" s="23">
+        <f>39296/42/24</f>
+        <v>38.984126984126981</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="C11" s="16">
+        <v>256</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="I11" s="7">
+        <f>84672/42/24</f>
+        <v>84</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C12" s="16">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="C13" s="16">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" s="16">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C15" s="16">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="C18" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C19" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C20" s="16">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="16">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C23" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="C24" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="C25" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="C26" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="C27" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="C28" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="C29" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C30" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="C31" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="C32" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="C33" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="C34" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="C35" s="16">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="C36" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="C37" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="C38" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="C39" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="C40" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="C41" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="C42" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="C43" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="C44" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C45" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="C46" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="C47" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="C48" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="C49" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="C50" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="C51" s="17">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="C52" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="C53" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="C54" s="16">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="C55" s="16">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="C56" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="C57" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="C58" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="C59" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="C60" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="C61" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C62" s="19">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="C63" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="C64" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="C65" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="C66" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="C67" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="C68" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="C69" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="C70" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="C71" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="C72" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="C73" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="C74" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="C75" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="C76" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="C77" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="C78" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="C79" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="C80" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="C81" s="19">
+        <v>4076</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="C82" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B83" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="C83" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B84" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="C84" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B85" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="C85" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B86" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="C86" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B87" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="C87" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B88" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="C88" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B89" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="C89" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B90" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="C90" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="C91" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B92" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="C92" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B93" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="C93" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B94" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="C94" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B95" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="C95" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B96" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="C96" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B97" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="C97" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B98" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="C98" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B99" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="C99" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B100" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="C100" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B101" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C101" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B102" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C102" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B103" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="C103" s="16">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{6b89535c-2ba5-4f71-a34a-075d8392d04a}" enabled="1" method="Privileged" siteId="{d4ffc887-d88d-41cc-bf6a-6bb47ec0f3ca}" contentBits="0" removed="0"/>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E565AA8E-565E-45A2-ACF3-F166F85F9BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D8714C-893E-4B4A-A96D-26610FA11574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14250" yWindow="615" windowWidth="11415" windowHeight="12330" firstSheet="4" activeTab="5" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
@@ -1133,7 +1133,7 @@
     <t>PK 및 기타 가열육 재고</t>
   </si>
   <si>
-    <t>재고 현황 요약</t>
+    <t>8월 1주 재고 현황 요약</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1143,7 @@
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1273,28 +1273,28 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1304,13 +1304,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D8714C-893E-4B4A-A96D-26610FA11574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3866E996-7263-49E7-83AD-3A8856760DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14250" yWindow="615" windowWidth="11415" windowHeight="12330" firstSheet="4" activeTab="5" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="인사및일정" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="364">
   <si>
     <t>이름</t>
   </si>
@@ -1134,6 +1134,9 @@
   </si>
   <si>
     <t>8월 1주 재고 현황 요약</t>
+  </si>
+  <si>
+    <t>OFF</t>
   </si>
 </sst>
 </file>
@@ -1741,7 +1744,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>3</v>
+        <v>363</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -4441,11 +4444,11 @@
       </c>
       <c r="F10" s="26">
         <f>C81</f>
-        <v>4076</v>
+        <v>5160</v>
       </c>
       <c r="G10" s="27">
         <f>F10/42</f>
-        <v>97.047619047619051</v>
+        <v>122.85714285714286</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>358</v>
@@ -5036,7 +5039,7 @@
         <v>326</v>
       </c>
       <c r="C81" s="19">
-        <v>4076</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3866E996-7263-49E7-83AD-3A8856760DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9B8265-196C-4D60-9BBE-BA010B9786CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="인사및일정" sheetId="1" r:id="rId1"/>
@@ -1821,7 +1821,7 @@
         <v>220</v>
       </c>
       <c r="I3" s="6">
-        <v>46244</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
@@ -2055,7 +2055,7 @@
         <v>47</v>
       </c>
       <c r="I12" s="6">
-        <v>46244</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9B8265-196C-4D60-9BBE-BA010B9786CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1ED0F5-71B9-4D28-A746-D01D38D30044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="인사및일정" sheetId="1" r:id="rId1"/>
@@ -1133,10 +1133,10 @@
     <t>PK 및 기타 가열육 재고</t>
   </si>
   <si>
-    <t>8월 1주 재고 현황 요약</t>
-  </si>
-  <si>
     <t>OFF</t>
+  </si>
+  <si>
+    <t>8월 2주 재고 현황 요약</t>
   </si>
 </sst>
 </file>
@@ -1744,7 +1744,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -4293,7 +4293,7 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="26.25" x14ac:dyDescent="0.25">

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1ED0F5-71B9-4D28-A746-D01D38D30044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF535F7-2D81-43BC-9153-FD974F402763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
-    <sheet name="인사및일정" sheetId="1" r:id="rId1"/>
-    <sheet name="재고현황" sheetId="2" r:id="rId2"/>
-    <sheet name="운영스케줄" sheetId="3" r:id="rId3"/>
-    <sheet name="소전각 가격" sheetId="4" r:id="rId4"/>
-    <sheet name="원부자재 구매액" sheetId="5" r:id="rId5"/>
-    <sheet name="월별 재고 요약" sheetId="6" r:id="rId6"/>
+    <sheet name="HR" sheetId="1" r:id="rId1"/>
+    <sheet name="Major Item" sheetId="2" r:id="rId2"/>
+    <sheet name="OB Schedule" sheetId="3" r:id="rId3"/>
+    <sheet name="Beef Clod" sheetId="4" r:id="rId4"/>
+    <sheet name="Purchasing Amount" sheetId="5" r:id="rId5"/>
+    <sheet name="Inventory Summary" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,68 +44,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="364">
-  <si>
-    <t>이름</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="347">
   <si>
     <t>직급</t>
   </si>
   <si>
-    <t>담당업무</t>
-  </si>
-  <si>
-    <t>근무중</t>
-  </si>
-  <si>
-    <t>품목명</t>
-  </si>
-  <si>
-    <t>분류</t>
-  </si>
-  <si>
-    <t>현재재고</t>
-  </si>
-  <si>
-    <t>안전재고</t>
-  </si>
-  <si>
-    <t>발주일정</t>
-  </si>
-  <si>
-    <t>입고예정일</t>
-  </si>
-  <si>
-    <t>원재료</t>
-  </si>
-  <si>
-    <t>현재상태</t>
-  </si>
-  <si>
     <t>시작일</t>
   </si>
   <si>
     <t>종료일</t>
   </si>
   <si>
-    <t>비고</t>
-  </si>
-  <si>
     <t>구분</t>
   </si>
   <si>
-    <t>관련품목</t>
-  </si>
-  <si>
-    <t>수량</t>
-  </si>
-  <si>
-    <t>예정일</t>
-  </si>
-  <si>
-    <t>출고</t>
-  </si>
-  <si>
     <t>Purchasing, S&amp;R</t>
   </si>
   <si>
@@ -115,18 +67,6 @@
     <t>S&amp;R, Production</t>
   </si>
   <si>
-    <t>소전각</t>
-  </si>
-  <si>
-    <t>간장</t>
-  </si>
-  <si>
-    <t>설탕</t>
-  </si>
-  <si>
-    <t>공급처</t>
-  </si>
-  <si>
     <t>True West Beef</t>
   </si>
   <si>
@@ -136,36 +76,15 @@
     <t>United Salad</t>
   </si>
   <si>
-    <t>사과 퓨레</t>
-  </si>
-  <si>
-    <t>배 퓨레</t>
-  </si>
-  <si>
     <t>Fierce Fruit</t>
   </si>
   <si>
-    <t>파인애플 주스</t>
-  </si>
-  <si>
     <t>McDonald</t>
   </si>
   <si>
-    <t>트레이</t>
-  </si>
-  <si>
-    <t>TJ 슬리브</t>
-  </si>
-  <si>
-    <t>TJ 박스</t>
-  </si>
-  <si>
     <t>Point Five</t>
   </si>
   <si>
-    <t>부자재</t>
-  </si>
-  <si>
     <t>Ace Commercial</t>
   </si>
   <si>
@@ -175,21 +94,9 @@
     <t>2 FTL</t>
   </si>
   <si>
-    <t>마늘</t>
-  </si>
-  <si>
     <t>Wang Global</t>
   </si>
   <si>
-    <t>양파</t>
-  </si>
-  <si>
-    <t>미정</t>
-  </si>
-  <si>
-    <t>8월 초</t>
-  </si>
-  <si>
     <t>13 totes</t>
   </si>
   <si>
@@ -223,9 +130,6 @@
     <t>50 PLT</t>
   </si>
   <si>
-    <t>구매가격</t>
-  </si>
-  <si>
     <t>01/02/2026</t>
   </si>
   <si>
@@ -598,36 +502,12 @@
     <t>06/25/2026</t>
   </si>
   <si>
-    <t>날짜</t>
-  </si>
-  <si>
-    <t>시장 가격</t>
-  </si>
-  <si>
     <t>Trader Joe's</t>
   </si>
   <si>
     <t>1 FTL</t>
   </si>
   <si>
-    <t>Trader Joe's(J&amp;D)</t>
-  </si>
-  <si>
-    <t>273차 - 외부창고</t>
-  </si>
-  <si>
-    <t>274차 - 외부창고</t>
-  </si>
-  <si>
-    <t>277차 - 외부창고</t>
-  </si>
-  <si>
-    <t>276차 - 공장</t>
-  </si>
-  <si>
-    <t>278차 - 외부창고</t>
-  </si>
-  <si>
     <t>Lyons, Robert W</t>
   </si>
   <si>
@@ -640,42 +520,6 @@
     <t>Matthew(Insang) Joung</t>
   </si>
   <si>
-    <t>업무 제한: 20lb 이상 Lifting 금지</t>
-  </si>
-  <si>
-    <t>8월 말, 9월 말</t>
-  </si>
-  <si>
-    <t>발주 시점</t>
-  </si>
-  <si>
-    <t>매주 확인</t>
-  </si>
-  <si>
-    <t>매월 3주</t>
-  </si>
-  <si>
-    <t>매주 목요일</t>
-  </si>
-  <si>
-    <t>박스 수령일 -&gt; 다음달 발주</t>
-  </si>
-  <si>
-    <t>슬리브 수령일 -&gt; 다음달 발주</t>
-  </si>
-  <si>
-    <t>트레이 수령일 -&gt; 2달 후 발주</t>
-  </si>
-  <si>
-    <t>격주로 확인</t>
-  </si>
-  <si>
-    <t>280차 - 외부창고</t>
-  </si>
-  <si>
-    <t>279차 - 공장</t>
-  </si>
-  <si>
     <t>Remond</t>
   </si>
   <si>
@@ -685,18 +529,6 @@
     <t>LA Changtuh</t>
   </si>
   <si>
-    <t>282차 - 공장</t>
-  </si>
-  <si>
-    <t>281차 - 공장</t>
-  </si>
-  <si>
-    <t>284차 -외부창고</t>
-  </si>
-  <si>
-    <t>285차 - 공장</t>
-  </si>
-  <si>
     <t>Chunil</t>
   </si>
   <si>
@@ -715,79 +547,10 @@
     <t>8/6, 8/13, 8/20, 8/27</t>
   </si>
   <si>
-    <t>8월 중순</t>
-  </si>
-  <si>
-    <t>8/21 휴가 예정</t>
-  </si>
-  <si>
     <t>3 FTL</t>
   </si>
   <si>
     <t>1.2 FTL</t>
-  </si>
-  <si>
-    <t>2025년 전체</t>
-  </si>
-  <si>
-    <t>26년 1월</t>
-  </si>
-  <si>
-    <t>26년 2월</t>
-  </si>
-  <si>
-    <t>26년 3월</t>
-  </si>
-  <si>
-    <t>26년 4월</t>
-  </si>
-  <si>
-    <t>26년 5월</t>
-  </si>
-  <si>
-    <t>26년 6월</t>
-  </si>
-  <si>
-    <t>26년 7월</t>
-  </si>
-  <si>
-    <t>26년 8월</t>
-  </si>
-  <si>
-    <t>26년 9월</t>
-  </si>
-  <si>
-    <t>2026년 누적</t>
-  </si>
-  <si>
-    <t>2026년 월평균</t>
-  </si>
-  <si>
-    <t>2025년 월평균</t>
-  </si>
-  <si>
-    <t>26년 10월</t>
-  </si>
-  <si>
-    <t>26년 11월</t>
-  </si>
-  <si>
-    <t>26년 12월</t>
-  </si>
-  <si>
-    <t>시장가격 누계 평균</t>
-  </si>
-  <si>
-    <t>구매가격 누계평균</t>
-  </si>
-  <si>
-    <t>차이</t>
-  </si>
-  <si>
-    <t>누계 구매량</t>
-  </si>
-  <si>
-    <t>283차 - 외부창고</t>
   </si>
   <si>
     <t>Kroger</t>
@@ -1094,49 +857,235 @@
     <t>PK 홍합미역국</t>
   </si>
   <si>
-    <t>박스</t>
-  </si>
-  <si>
-    <t>팔렛</t>
-  </si>
-  <si>
-    <t>PK 국탕류 재고</t>
-  </si>
-  <si>
-    <t>한상 국탕류 재고</t>
-  </si>
-  <si>
-    <t>Kroger 소불고기 재고</t>
-  </si>
-  <si>
-    <t>TJ 소불고기 재고</t>
-  </si>
-  <si>
-    <t>국탕류 100개 미만 품목</t>
-  </si>
-  <si>
-    <t>국탕류 300개 이상 품목</t>
-  </si>
-  <si>
-    <t>특이사항</t>
-  </si>
-  <si>
-    <t>공장</t>
-  </si>
-  <si>
-    <t>외부창고</t>
-  </si>
-  <si>
-    <t>건</t>
-  </si>
-  <si>
-    <t>PK 및 기타 가열육 재고</t>
-  </si>
-  <si>
     <t>OFF</t>
   </si>
   <si>
-    <t>8월 2주 재고 현황 요약</t>
+    <t>On</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Limitation: No Lift over 20 lbs</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Package</t>
+  </si>
+  <si>
+    <t>Food/Package</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Beef Clod</t>
+  </si>
+  <si>
+    <t>Soy Sauce</t>
+  </si>
+  <si>
+    <t>Sugar</t>
+  </si>
+  <si>
+    <t>Apple Puree</t>
+  </si>
+  <si>
+    <t>Pear Puree</t>
+  </si>
+  <si>
+    <t>Pineapple Juice</t>
+  </si>
+  <si>
+    <t>Garlic</t>
+  </si>
+  <si>
+    <t>Onion</t>
+  </si>
+  <si>
+    <t>Tray</t>
+  </si>
+  <si>
+    <t>TJ Sleeves</t>
+  </si>
+  <si>
+    <t>TJ Boxes</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Current stock</t>
+  </si>
+  <si>
+    <t>Safety Stock</t>
+  </si>
+  <si>
+    <t>Inventory Checking</t>
+  </si>
+  <si>
+    <t>Every week</t>
+  </si>
+  <si>
+    <t>Every 3rd week</t>
+  </si>
+  <si>
+    <t>Every Thursday</t>
+  </si>
+  <si>
+    <t>Bi weekly</t>
+  </si>
+  <si>
+    <t>Receiving date -&gt; order for 2 months later</t>
+  </si>
+  <si>
+    <t>Receiving date -&gt; order for next month</t>
+  </si>
+  <si>
+    <t>Estimated Receiving Date</t>
+  </si>
+  <si>
+    <t>Middle of Aug</t>
+  </si>
+  <si>
+    <t>Not confirmed</t>
+  </si>
+  <si>
+    <t>End of Aug, End of Sep</t>
+  </si>
+  <si>
+    <t>Begining of Aug</t>
+  </si>
+  <si>
+    <t>Order Date</t>
+  </si>
+  <si>
+    <t>Outbound</t>
+  </si>
+  <si>
+    <t>Customoer</t>
+  </si>
+  <si>
+    <t>Move to J&amp;D</t>
+  </si>
+  <si>
+    <t>Qt</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>285 - Factory</t>
+  </si>
+  <si>
+    <t>281 - Factory</t>
+  </si>
+  <si>
+    <t>282 - Factory</t>
+  </si>
+  <si>
+    <t>279 - Factory</t>
+  </si>
+  <si>
+    <t>276 - Factory</t>
+  </si>
+  <si>
+    <t>273 - J&amp;D</t>
+  </si>
+  <si>
+    <t>274 - J&amp;D</t>
+  </si>
+  <si>
+    <t>277 - J&amp;D</t>
+  </si>
+  <si>
+    <t>278 - J&amp;D</t>
+  </si>
+  <si>
+    <t>280 - J&amp;D</t>
+  </si>
+  <si>
+    <t>284 -J&amp;D</t>
+  </si>
+  <si>
+    <t>283 - J&amp;D</t>
+  </si>
+  <si>
+    <t>Market Price</t>
+  </si>
+  <si>
+    <t>Purchasing Price</t>
+  </si>
+  <si>
+    <t>Avg MP</t>
+  </si>
+  <si>
+    <t>Avg PP</t>
+  </si>
+  <si>
+    <t>Diff</t>
+  </si>
+  <si>
+    <t>Purchasing Qt</t>
+  </si>
+  <si>
+    <t>2025 Monthly Avg</t>
+  </si>
+  <si>
+    <t>2026 Monthly Avg</t>
+  </si>
+  <si>
+    <t>2025 Cumulative</t>
+  </si>
+  <si>
+    <t>2026 Cumulative</t>
+  </si>
+  <si>
+    <t>2nd week of Aug, Inventory</t>
+  </si>
+  <si>
+    <t>PK Soup</t>
+  </si>
+  <si>
+    <t>HS Soup</t>
+  </si>
+  <si>
+    <t>PK + ETC BBQ</t>
+  </si>
+  <si>
+    <t>Kroger Beef Bulgogi</t>
+  </si>
+  <si>
+    <t>TJ Beef Bulgogi</t>
+  </si>
+  <si>
+    <t>SSG</t>
+  </si>
+  <si>
+    <t>J&amp;D</t>
+  </si>
+  <si>
+    <t>under 100 cs</t>
+  </si>
+  <si>
+    <t>over 300 cs</t>
+  </si>
+  <si>
+    <t>cs</t>
+  </si>
+  <si>
+    <t>plt</t>
   </si>
 </sst>
 </file>
@@ -1243,7 +1192,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1316,6 +1265,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1667,54 +1617,52 @@
     <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>3</v>
+        <v>271</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="2" t="s">
-        <v>224</v>
-      </c>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="2:8" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>3</v>
+        <v>271</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -1722,14 +1670,14 @@
     </row>
     <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>3</v>
+        <v>271</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -1737,19 +1685,19 @@
     </row>
     <row r="6" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>362</v>
+        <v>270</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="2" t="s">
-        <v>198</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -1762,7 +1710,7 @@
   <dimension ref="B2:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -1772,53 +1720,53 @@
     <col min="10" max="10" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>279</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>4</v>
+        <v>280</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>26</v>
+        <v>292</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>6</v>
+        <v>293</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>7</v>
+        <v>294</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>200</v>
+        <v>295</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>9</v>
+        <v>302</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>277</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>23</v>
+        <v>281</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>201</v>
+        <v>296</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>220</v>
+        <v>164</v>
       </c>
       <c r="I3" s="6">
         <v>46249</v>
@@ -1826,25 +1774,25 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>277</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>24</v>
+        <v>282</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>202</v>
+        <v>297</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="I4" s="6">
         <v>46254</v>
@@ -1852,25 +1800,25 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>277</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>25</v>
+        <v>283</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>203</v>
+        <v>298</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="I5" s="6">
         <v>46258</v>
@@ -1878,25 +1826,25 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>202</v>
+        <v>297</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>223</v>
+        <v>303</v>
       </c>
       <c r="I6" s="6">
         <v>46254</v>
@@ -1904,51 +1852,51 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>202</v>
+        <v>297</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>223</v>
+        <v>303</v>
       </c>
       <c r="I7" s="6">
         <v>46254</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>277</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>33</v>
+        <v>286</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>207</v>
+        <v>299</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>46</v>
+        <v>304</v>
       </c>
       <c r="I8" s="6">
         <v>46251</v>
@@ -1956,25 +1904,25 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>277</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>43</v>
+        <v>287</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>202</v>
+        <v>297</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>46</v>
+        <v>304</v>
       </c>
       <c r="I9" s="6">
         <v>46254</v>
@@ -1982,51 +1930,51 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>10</v>
+        <v>277</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>203</v>
+        <v>298</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="I10" s="6">
         <v>46258</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>35</v>
+        <v>289</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>206</v>
+        <v>300</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="I11" s="6">
         <v>46260</v>
@@ -2034,25 +1982,25 @@
     </row>
     <row r="12" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>205</v>
+        <v>301</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>47</v>
+        <v>306</v>
       </c>
       <c r="I12" s="6">
         <v>46249</v>
@@ -2060,22 +2008,22 @@
     </row>
     <row r="13" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>37</v>
+        <v>291</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>204</v>
+        <v>301</v>
       </c>
       <c r="H13" s="6">
         <v>46262</v>
@@ -2103,30 +2051,30 @@
     <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>308</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>309</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>311</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>312</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>188</v>
+        <v>310</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E3" s="3">
         <v>46217</v>
@@ -2135,81 +2083,81 @@
     </row>
     <row r="4" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E4" s="3">
         <v>46218</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E5" s="3">
         <v>46223</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>190</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E6" s="3">
         <v>46225</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>192</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E7" s="3">
         <v>46226</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>191</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>188</v>
+        <v>310</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E8" s="3">
         <v>46232</v>
@@ -2218,47 +2166,47 @@
     </row>
     <row r="9" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E9" s="3">
         <v>46234</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>193</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E10" s="3">
         <v>46237</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>209</v>
+        <v>316</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="E11" s="3">
         <v>46223</v>
@@ -2267,13 +2215,13 @@
     </row>
     <row r="12" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="E12" s="3">
         <v>46223</v>
@@ -2282,30 +2230,30 @@
     </row>
     <row r="13" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E13" s="3">
         <v>46238</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>208</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E14" s="3">
         <v>46239</v>
@@ -2314,13 +2262,13 @@
     </row>
     <row r="15" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>188</v>
+        <v>310</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E15" s="3">
         <v>46241</v>
@@ -2329,64 +2277,64 @@
     </row>
     <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E16" s="3">
         <v>46245</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>213</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E17" s="3">
         <v>46251</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>214</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E18" s="3">
         <v>46251</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>215</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>188</v>
+        <v>310</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E19" s="3">
         <v>46253</v>
@@ -2395,30 +2343,30 @@
     </row>
     <row r="20" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E20" s="3">
         <v>46258</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>216</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="E21" s="3">
         <v>46251</v>
@@ -2427,13 +2375,13 @@
     </row>
     <row r="22" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>219</v>
+        <v>163</v>
       </c>
       <c r="E22" s="3">
         <v>46261</v>
@@ -2442,30 +2390,30 @@
     </row>
     <row r="23" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E23" s="3">
         <v>46252</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>247</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>19</v>
+        <v>308</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="E24" s="3">
         <v>46245</v>
@@ -2547,25 +2495,25 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
-        <v>184</v>
+        <v>312</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>185</v>
+        <v>325</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>59</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C3" s="8">
         <v>4.13</v>
       </c>
       <c r="D3" s="8"/>
       <c r="G3" s="11" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="H3" s="12">
         <v>4.4000000000000004</v>
@@ -2573,14 +2521,14 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C4" s="8">
         <v>4.1099999999999994</v>
       </c>
       <c r="D4" s="8"/>
       <c r="G4" s="11" t="s">
-        <v>244</v>
+        <v>328</v>
       </c>
       <c r="H4" s="12">
         <f>AVERAGE(D3:D155)</f>
@@ -2589,7 +2537,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C5" s="8">
         <v>4.1999999999999993</v>
@@ -2598,7 +2546,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>245</v>
+        <v>329</v>
       </c>
       <c r="H5" s="13">
         <f>(H4-H3)/H3</f>
@@ -2607,14 +2555,14 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="C6" s="8">
         <v>4.2199999999999989</v>
       </c>
       <c r="D6" s="8"/>
       <c r="G6" s="11" t="s">
-        <v>246</v>
+        <v>330</v>
       </c>
       <c r="H6" s="11" t="str">
         <f>COUNT(D3:D370)&amp;"FTL"</f>
@@ -2623,7 +2571,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="C7" s="8">
         <v>4.1599999999999993</v>
@@ -2632,7 +2580,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="C8" s="8">
         <v>4.2399999999999993</v>
@@ -2641,7 +2589,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="C9" s="8">
         <v>4.2799999999999994</v>
@@ -2650,7 +2598,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="C10" s="8">
         <v>4.2399999999999993</v>
@@ -2661,7 +2609,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C11" s="8">
         <v>4.1999999999999993</v>
@@ -2670,7 +2618,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="C12" s="8">
         <v>4.2299999999999995</v>
@@ -2681,7 +2629,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="C13" s="8">
         <v>4.1599999999999993</v>
@@ -2690,7 +2638,7 @@
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="C14" s="8">
         <v>4.3099999999999996</v>
@@ -2699,7 +2647,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="C15" s="8">
         <v>4.2399999999999993</v>
@@ -2710,7 +2658,7 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="C16" s="8">
         <v>4.2799999999999994</v>
@@ -2719,7 +2667,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="C17" s="8">
         <v>4.3299999999999992</v>
@@ -2728,7 +2676,7 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C18" s="8">
         <v>4.339999999999999</v>
@@ -2737,7 +2685,7 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="C19" s="8">
         <v>4.3299999999999992</v>
@@ -2746,7 +2694,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="C20" s="8">
         <v>4.2399999999999993</v>
@@ -2755,7 +2703,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C21" s="8">
         <v>4.2199999999999989</v>
@@ -2764,7 +2712,7 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="C22" s="8">
         <v>4.2199999999999989</v>
@@ -2773,7 +2721,7 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="C23" s="8">
         <v>4.2799999999999994</v>
@@ -2782,7 +2730,7 @@
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="C24" s="8">
         <v>4.3299999999999992</v>
@@ -2793,7 +2741,7 @@
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="C25" s="8">
         <v>4.3099999999999996</v>
@@ -2802,7 +2750,7 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="C26" s="8">
         <v>4.2499999999999991</v>
@@ -2813,7 +2761,7 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="C27" s="8">
         <v>4.2699999999999996</v>
@@ -2822,7 +2770,7 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="C28" s="8">
         <v>4.2699999999999996</v>
@@ -2833,7 +2781,7 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="C29" s="8">
         <v>4.3099999999999996</v>
@@ -2842,7 +2790,7 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="C30" s="8">
         <v>4.2299999999999995</v>
@@ -2853,7 +2801,7 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="C31" s="8">
         <v>4.2299999999999995</v>
@@ -2862,7 +2810,7 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C32" s="8">
         <v>4.18</v>
@@ -2873,7 +2821,7 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="C33" s="8">
         <v>4.2599999999999989</v>
@@ -2882,7 +2830,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C34" s="8">
         <v>4.2699999999999996</v>
@@ -2891,7 +2839,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="C35" s="8">
         <v>4.2599999999999989</v>
@@ -2900,7 +2848,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="C36" s="8">
         <v>4.2399999999999993</v>
@@ -2911,7 +2859,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="7" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="C37" s="8">
         <v>4.2899999999999991</v>
@@ -2920,7 +2868,7 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="7" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="C38" s="8">
         <v>4.2899999999999991</v>
@@ -2929,7 +2877,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="7" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="C39" s="8">
         <v>4.3099999999999996</v>
@@ -2938,7 +2886,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="C40" s="8">
         <v>4.3899999999999997</v>
@@ -2949,7 +2897,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="7" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="C41" s="8">
         <v>4.4099999999999993</v>
@@ -2958,7 +2906,7 @@
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="C42" s="8">
         <v>4.419999999999999</v>
@@ -2969,7 +2917,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="C43" s="8">
         <v>4.4499999999999993</v>
@@ -2978,7 +2926,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C44" s="8">
         <v>4.4699999999999989</v>
@@ -2987,7 +2935,7 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="C45" s="8">
         <v>4.4799999999999995</v>
@@ -2996,7 +2944,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="C46" s="8">
         <v>4.4899999999999993</v>
@@ -3005,7 +2953,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C47" s="8">
         <v>4.669999999999999</v>
@@ -3016,7 +2964,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="C48" s="8">
         <v>4.5799999999999992</v>
@@ -3025,7 +2973,7 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="C49" s="8">
         <v>4.669999999999999</v>
@@ -3034,7 +2982,7 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="7" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="C50" s="8">
         <v>4.5699999999999994</v>
@@ -3045,7 +2993,7 @@
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="7" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="C51" s="8">
         <v>4.589999999999999</v>
@@ -3054,7 +3002,7 @@
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="7" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="C52" s="8">
         <v>4.5499999999999989</v>
@@ -3065,7 +3013,7 @@
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="7" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="C53" s="8">
         <v>4.7199999999999989</v>
@@ -3074,7 +3022,7 @@
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54" s="7" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C54" s="8">
         <v>4.6399999999999997</v>
@@ -3083,7 +3031,7 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="C55" s="8">
         <v>4.6499999999999995</v>
@@ -3094,7 +3042,7 @@
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="C56" s="8">
         <v>4.6399999999999997</v>
@@ -3103,7 +3051,7 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="7" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="C57" s="8">
         <v>4.6099999999999994</v>
@@ -3114,7 +3062,7 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="7" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C58" s="8">
         <v>4.5299999999999994</v>
@@ -3125,7 +3073,7 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="7" t="s">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="C59" s="8">
         <v>4.6599999999999993</v>
@@ -3134,7 +3082,7 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="7" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C60" s="8">
         <v>4.4999999999999991</v>
@@ -3143,7 +3091,7 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="7" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="C61" s="8">
         <v>4.5599999999999996</v>
@@ -3152,7 +3100,7 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="7" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C62" s="8">
         <v>4.5299999999999994</v>
@@ -3163,7 +3111,7 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="7" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="C63" s="8">
         <v>4.5099999999999989</v>
@@ -3172,7 +3120,7 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="7" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="C64" s="8">
         <v>4.5499999999999989</v>
@@ -3181,7 +3129,7 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="7" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="C65" s="8">
         <v>4.5099999999999989</v>
@@ -3190,7 +3138,7 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="7" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C66" s="8">
         <v>4.4599999999999991</v>
@@ -3199,7 +3147,7 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="7" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="C67" s="8">
         <v>4.4499999999999993</v>
@@ -3208,7 +3156,7 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="7" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="C68" s="8">
         <v>4.4499999999999993</v>
@@ -3219,7 +3167,7 @@
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="7" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C69" s="8">
         <v>4.3999999999999995</v>
@@ -3228,7 +3176,7 @@
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="7" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C70" s="8">
         <v>4.3599999999999994</v>
@@ -3237,7 +3185,7 @@
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="7" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C71" s="8">
         <v>4.3599999999999994</v>
@@ -3248,7 +3196,7 @@
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="7" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="C72" s="8">
         <v>4.2599999999999989</v>
@@ -3257,7 +3205,7 @@
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="7" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="C73" s="8">
         <v>4.2299999999999995</v>
@@ -3268,7 +3216,7 @@
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="7" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="C74" s="8">
         <v>4.2499999999999991</v>
@@ -3277,7 +3225,7 @@
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="7" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="C75" s="8">
         <v>4.2199999999999989</v>
@@ -3286,7 +3234,7 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="7" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="C76" s="8">
         <v>4.2499999999999991</v>
@@ -3297,7 +3245,7 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="7" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="C77" s="8">
         <v>4.2599999999999989</v>
@@ -3306,7 +3254,7 @@
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="7" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="C78" s="8">
         <v>4.2699999999999996</v>
@@ -3317,7 +3265,7 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="7" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="C79" s="8">
         <v>4.17</v>
@@ -3326,7 +3274,7 @@
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="7" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="C80" s="8">
         <v>4.2399999999999993</v>
@@ -3335,7 +3283,7 @@
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="7" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="C81" s="8">
         <v>4.2399999999999993</v>
@@ -3346,7 +3294,7 @@
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="7" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="C82" s="8">
         <v>4.2499999999999991</v>
@@ -3355,7 +3303,7 @@
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="7" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="C83" s="8">
         <v>4.2799999999999994</v>
@@ -3366,7 +3314,7 @@
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" s="7" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="C84" s="8">
         <v>4.3099999999999996</v>
@@ -3375,7 +3323,7 @@
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="7" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="C85" s="8">
         <v>4.2899999999999991</v>
@@ -3384,7 +3332,7 @@
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="7" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="C86" s="8">
         <v>4.3199999999999994</v>
@@ -3395,7 +3343,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="7" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="C87" s="8">
         <v>4.419999999999999</v>
@@ -3404,7 +3352,7 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="7" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="C88" s="8">
         <v>4.3699999999999992</v>
@@ -3415,7 +3363,7 @@
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="7" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="C89" s="8">
         <v>4.3699999999999992</v>
@@ -3424,7 +3372,7 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="7" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="C90" s="8">
         <v>4.379999999999999</v>
@@ -3433,7 +3381,7 @@
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="7" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="C91" s="8">
         <v>4.3899999999999997</v>
@@ -3442,7 +3390,7 @@
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92" s="7" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="C92" s="8">
         <v>4.43</v>
@@ -3451,7 +3399,7 @@
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93" s="7" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="C93" s="8">
         <v>4.3099999999999996</v>
@@ -3462,7 +3410,7 @@
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B94" s="7" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="C94" s="8">
         <v>4.3899999999999997</v>
@@ -3471,7 +3419,7 @@
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B95" s="7" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="C95" s="8">
         <v>4.4399999999999995</v>
@@ -3480,7 +3428,7 @@
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B96" s="7" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="C96" s="8">
         <v>4.3999999999999995</v>
@@ -3489,7 +3437,7 @@
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="7" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C97" s="8">
         <v>4.4399999999999995</v>
@@ -3498,7 +3446,7 @@
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" s="7" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C98" s="8">
         <v>4.379999999999999</v>
@@ -3509,7 +3457,7 @@
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" s="7" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="C99" s="8">
         <v>4.4599999999999991</v>
@@ -3518,7 +3466,7 @@
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100" s="7" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="C100" s="8">
         <v>4.419999999999999</v>
@@ -3527,7 +3475,7 @@
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101" s="7" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="C101" s="8">
         <v>4.5199999999999996</v>
@@ -3538,7 +3486,7 @@
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102" s="7" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="C102" s="8">
         <v>4.4399999999999995</v>
@@ -3547,7 +3495,7 @@
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103" s="7" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="C103" s="8">
         <v>4.5399999999999991</v>
@@ -3556,7 +3504,7 @@
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="7" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="C104" s="8">
         <v>4.4799999999999995</v>
@@ -3565,7 +3513,7 @@
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="7" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="C105" s="8">
         <v>4.5299999999999994</v>
@@ -3576,7 +3524,7 @@
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106" s="7" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="C106" s="8">
         <v>4.4899999999999993</v>
@@ -3585,7 +3533,7 @@
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107" s="7" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="C107" s="8">
         <v>4.4999999999999991</v>
@@ -3596,7 +3544,7 @@
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108" s="7" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="C108" s="8">
         <v>4.5799999999999992</v>
@@ -3605,7 +3553,7 @@
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109" s="7" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="C109" s="8">
         <v>4.5699999999999994</v>
@@ -3614,7 +3562,7 @@
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" s="7" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="C110" s="8">
         <v>4.4699999999999989</v>
@@ -3625,7 +3573,7 @@
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="7" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="C111" s="8">
         <v>4.379999999999999</v>
@@ -3634,7 +3582,7 @@
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="7" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="C112" s="8">
         <v>4.589999999999999</v>
@@ -3645,7 +3593,7 @@
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="7" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="C113" s="8">
         <v>4.6399999999999997</v>
@@ -3654,7 +3602,7 @@
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="7" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="C114" s="8">
         <v>4.5099999999999989</v>
@@ -3663,7 +3611,7 @@
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="7" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="C115" s="8">
         <v>4.5299999999999994</v>
@@ -3672,7 +3620,7 @@
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116" s="7" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="C116" s="8">
         <v>4.5599999999999996</v>
@@ -3681,7 +3629,7 @@
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117" s="7" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="C117" s="8">
         <v>4.6499999999999995</v>
@@ -3690,7 +3638,7 @@
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118" s="7" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="C118" s="8">
         <v>4.5599999999999996</v>
@@ -3699,7 +3647,7 @@
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B119" s="7" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="C119" s="8">
         <v>4.6499999999999995</v>
@@ -3710,7 +3658,7 @@
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120" s="7" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="C120" s="8">
         <v>4.5999999999999996</v>
@@ -3719,7 +3667,7 @@
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B121" s="7" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="C121" s="8">
         <v>4.6099999999999994</v>
@@ -3728,7 +3676,7 @@
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B122" s="7" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C122" s="8">
         <v>4.6599999999999993</v>
@@ -3737,7 +3685,7 @@
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B123" s="7" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="C123" s="8">
         <v>4.5999999999999996</v>
@@ -3748,7 +3696,7 @@
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124" s="7" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="C124" s="8">
         <v>4.629999999999999</v>
@@ -3757,7 +3705,7 @@
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B125" s="7" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="C125" s="8">
         <v>4.6099999999999994</v>
@@ -3766,7 +3714,7 @@
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126" s="7" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
       <c r="C126" s="8">
         <v>4.669999999999999</v>
@@ -3775,7 +3723,7 @@
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B127" s="7" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="C127" s="8">
         <v>4.5599999999999996</v>
@@ -4106,25 +4054,23 @@
   <dimension ref="C3:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C3" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="C3" s="7"/>
       <c r="D3" s="7" t="s">
-        <v>10</v>
+        <v>277</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C4" s="7" t="s">
-        <v>227</v>
+        <v>333</v>
       </c>
       <c r="D4" s="8">
         <v>15520853.789999999</v>
@@ -4135,7 +4081,7 @@
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C5" s="7" t="s">
-        <v>239</v>
+        <v>331</v>
       </c>
       <c r="D5" s="8">
         <f>D4/12</f>
@@ -4148,7 +4094,7 @@
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C6" s="7" t="s">
-        <v>237</v>
+        <v>334</v>
       </c>
       <c r="D6" s="8">
         <v>8817263.6600000001</v>
@@ -4159,7 +4105,7 @@
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C7" s="7" t="s">
-        <v>238</v>
+        <v>332</v>
       </c>
       <c r="D7" s="8">
         <f>D6/7</f>
@@ -4171,8 +4117,8 @@
       </c>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>228</v>
+      <c r="C8" s="28">
+        <v>46023</v>
       </c>
       <c r="D8" s="10">
         <v>1325698.24</v>
@@ -4182,8 +4128,8 @@
       </c>
     </row>
     <row r="9" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>229</v>
+      <c r="C9" s="28">
+        <v>46054</v>
       </c>
       <c r="D9" s="10">
         <v>1188990.72</v>
@@ -4193,8 +4139,8 @@
       </c>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>230</v>
+      <c r="C10" s="28">
+        <v>46082</v>
       </c>
       <c r="D10" s="10">
         <v>1614650.34</v>
@@ -4204,8 +4150,8 @@
       </c>
     </row>
     <row r="11" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>231</v>
+      <c r="C11" s="28">
+        <v>46113</v>
       </c>
       <c r="D11" s="10">
         <v>1403205.37</v>
@@ -4215,8 +4161,8 @@
       </c>
     </row>
     <row r="12" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
-        <v>232</v>
+      <c r="C12" s="28">
+        <v>46143</v>
       </c>
       <c r="D12" s="10">
         <v>1183673.21</v>
@@ -4226,8 +4172,8 @@
       </c>
     </row>
     <row r="13" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>233</v>
+      <c r="C13" s="28">
+        <v>46174</v>
       </c>
       <c r="D13" s="10">
         <v>1289298.07</v>
@@ -4237,8 +4183,8 @@
       </c>
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>234</v>
+      <c r="C14" s="28">
+        <v>46204</v>
       </c>
       <c r="D14" s="10">
         <v>811747.71</v>
@@ -4248,28 +4194,28 @@
       </c>
     </row>
     <row r="15" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
-        <v>235</v>
+      <c r="C15" s="28">
+        <v>46235</v>
       </c>
     </row>
     <row r="16" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>236</v>
+      <c r="C16" s="28">
+        <v>46266</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>240</v>
+      <c r="C17" s="28">
+        <v>46296</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C18" t="s">
-        <v>241</v>
+      <c r="C18" s="28">
+        <v>46327</v>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>242</v>
+      <c r="C19" s="28">
+        <v>46357</v>
       </c>
     </row>
   </sheetData>
@@ -4284,7 +4230,7 @@
   <cols>
     <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -4293,40 +4239,38 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>363</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>15</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="E4" s="20"/>
       <c r="F4" s="20" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>357</v>
+        <v>275</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="15" t="s">
-        <v>250</v>
+        <v>171</v>
       </c>
       <c r="C5" s="16">
         <v>275</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="F5" s="25">
         <f>SUM(C5:C35)</f>
@@ -4337,19 +4281,17 @@
         <v>61.322222222222223</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="I5" s="7">
         <f>COUNTIF(C5:C15,"&lt;100")+COUNTIF(C20:C21,"&lt;100")</f>
         <v>0</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>360</v>
-      </c>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
-        <v>251</v>
+        <v>172</v>
       </c>
       <c r="C6" s="16">
         <v>248</v>
@@ -4358,25 +4300,23 @@
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
       <c r="H6" s="7" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="I6" s="7">
         <f>COUNTIF(C5:C15,"&gt;300")+COUNTIF(C20:C21,"&gt;300")</f>
         <v>4</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>360</v>
-      </c>
+      <c r="J6" s="7"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="C7" s="16">
         <v>370</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="F7" s="20">
         <v>0</v>
@@ -4390,13 +4330,13 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
-        <v>253</v>
+        <v>174</v>
       </c>
       <c r="C8" s="16">
         <v>258</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="F8" s="20">
         <f>SUM(C49:C56)</f>
@@ -4412,13 +4352,13 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="15" t="s">
-        <v>254</v>
+        <v>175</v>
       </c>
       <c r="C9" s="16">
         <v>283</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="F9" s="22">
         <f>C62</f>
@@ -4434,13 +4374,13 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
-        <v>255</v>
+        <v>176</v>
       </c>
       <c r="C10" s="16">
         <v>318</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="F10" s="26">
         <f>C81</f>
@@ -4451,19 +4391,19 @@
         <v>122.85714285714286</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="I10" s="23">
         <f>39296/42/24</f>
         <v>38.984126984126981</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="15" t="s">
-        <v>256</v>
+        <v>177</v>
       </c>
       <c r="C11" s="16">
         <v>256</v>
@@ -4472,19 +4412,19 @@
       <c r="F11" s="26"/>
       <c r="G11" s="27"/>
       <c r="H11" s="7" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="I11" s="7">
         <f>84672/42/24</f>
         <v>84</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
-        <v>257</v>
+        <v>178</v>
       </c>
       <c r="C12" s="16">
         <v>241</v>
@@ -4492,7 +4432,7 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="15" t="s">
-        <v>258</v>
+        <v>179</v>
       </c>
       <c r="C13" s="16">
         <v>201</v>
@@ -4500,7 +4440,7 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>259</v>
+        <v>180</v>
       </c>
       <c r="C14" s="16">
         <v>256</v>
@@ -4508,7 +4448,7 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
-        <v>260</v>
+        <v>181</v>
       </c>
       <c r="C15" s="16">
         <v>269</v>
@@ -4516,7 +4456,7 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
-        <v>261</v>
+        <v>182</v>
       </c>
       <c r="C16" s="16">
         <v>0</v>
@@ -4524,7 +4464,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>262</v>
+        <v>183</v>
       </c>
       <c r="C17" s="16">
         <v>0</v>
@@ -4532,7 +4472,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>263</v>
+        <v>184</v>
       </c>
       <c r="C18" s="16">
         <v>0</v>
@@ -4540,7 +4480,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="C19" s="16">
         <v>0</v>
@@ -4548,7 +4488,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>265</v>
+        <v>186</v>
       </c>
       <c r="C20" s="16">
         <v>322</v>
@@ -4556,7 +4496,7 @@
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>266</v>
+        <v>187</v>
       </c>
       <c r="C21" s="16">
         <v>379</v>
@@ -4564,7 +4504,7 @@
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>267</v>
+        <v>188</v>
       </c>
       <c r="C22" s="16">
         <v>0</v>
@@ -4572,7 +4512,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>268</v>
+        <v>189</v>
       </c>
       <c r="C23" s="16">
         <v>0</v>
@@ -4580,7 +4520,7 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
-        <v>269</v>
+        <v>190</v>
       </c>
       <c r="C24" s="16">
         <v>0</v>
@@ -4588,7 +4528,7 @@
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
-        <v>270</v>
+        <v>191</v>
       </c>
       <c r="C25" s="16">
         <v>0</v>
@@ -4596,7 +4536,7 @@
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
-        <v>271</v>
+        <v>192</v>
       </c>
       <c r="C26" s="16">
         <v>0</v>
@@ -4604,7 +4544,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
-        <v>272</v>
+        <v>193</v>
       </c>
       <c r="C27" s="16">
         <v>0</v>
@@ -4612,7 +4552,7 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
-        <v>273</v>
+        <v>194</v>
       </c>
       <c r="C28" s="16">
         <v>0</v>
@@ -4620,7 +4560,7 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
-        <v>274</v>
+        <v>195</v>
       </c>
       <c r="C29" s="16">
         <v>0</v>
@@ -4628,7 +4568,7 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
-        <v>275</v>
+        <v>196</v>
       </c>
       <c r="C30" s="16">
         <v>0</v>
@@ -4636,7 +4576,7 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
-        <v>276</v>
+        <v>197</v>
       </c>
       <c r="C31" s="16">
         <v>0</v>
@@ -4644,7 +4584,7 @@
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
-        <v>277</v>
+        <v>198</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4652,7 +4592,7 @@
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
-        <v>278</v>
+        <v>199</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4660,7 +4600,7 @@
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
-        <v>279</v>
+        <v>200</v>
       </c>
       <c r="C34" s="16">
         <v>0</v>
@@ -4668,7 +4608,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
-        <v>280</v>
+        <v>201</v>
       </c>
       <c r="C35" s="16">
         <v>462</v>
@@ -4676,7 +4616,7 @@
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="C36" s="16">
         <v>0</v>
@@ -4684,7 +4624,7 @@
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
-        <v>282</v>
+        <v>203</v>
       </c>
       <c r="C37" s="16">
         <v>0</v>
@@ -4692,7 +4632,7 @@
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
-        <v>283</v>
+        <v>204</v>
       </c>
       <c r="C38" s="17">
         <v>0</v>
@@ -4700,7 +4640,7 @@
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
-        <v>284</v>
+        <v>205</v>
       </c>
       <c r="C39" s="16">
         <v>0</v>
@@ -4708,7 +4648,7 @@
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
-        <v>285</v>
+        <v>206</v>
       </c>
       <c r="C40" s="17">
         <v>0</v>
@@ -4716,7 +4656,7 @@
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
-        <v>286</v>
+        <v>207</v>
       </c>
       <c r="C41" s="17">
         <v>0</v>
@@ -4724,7 +4664,7 @@
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
-        <v>287</v>
+        <v>208</v>
       </c>
       <c r="C42" s="17">
         <v>0</v>
@@ -4732,7 +4672,7 @@
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
-        <v>288</v>
+        <v>209</v>
       </c>
       <c r="C43" s="17">
         <v>0</v>
@@ -4740,7 +4680,7 @@
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
-        <v>289</v>
+        <v>210</v>
       </c>
       <c r="C44" s="16">
         <v>0</v>
@@ -4748,7 +4688,7 @@
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
-        <v>290</v>
+        <v>211</v>
       </c>
       <c r="C45" s="16">
         <v>0</v>
@@ -4756,7 +4696,7 @@
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
-        <v>291</v>
+        <v>212</v>
       </c>
       <c r="C46" s="16">
         <v>0</v>
@@ -4764,7 +4704,7 @@
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
-        <v>292</v>
+        <v>213</v>
       </c>
       <c r="C47" s="16">
         <v>0</v>
@@ -4772,7 +4712,7 @@
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="s">
-        <v>293</v>
+        <v>214</v>
       </c>
       <c r="C48" s="16">
         <v>0</v>
@@ -4780,7 +4720,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
-        <v>294</v>
+        <v>215</v>
       </c>
       <c r="C49" s="16">
         <v>0</v>
@@ -4788,7 +4728,7 @@
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
-        <v>295</v>
+        <v>216</v>
       </c>
       <c r="C50" s="16">
         <v>0</v>
@@ -4796,7 +4736,7 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
-        <v>296</v>
+        <v>217</v>
       </c>
       <c r="C51" s="17">
         <v>78</v>
@@ -4804,7 +4744,7 @@
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="C52" s="16">
         <v>0</v>
@@ -4812,7 +4752,7 @@
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
-        <v>298</v>
+        <v>219</v>
       </c>
       <c r="C53" s="16">
         <v>0</v>
@@ -4820,7 +4760,7 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
-        <v>299</v>
+        <v>220</v>
       </c>
       <c r="C54" s="16">
         <v>160</v>
@@ -4828,7 +4768,7 @@
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="C55" s="16">
         <v>191</v>
@@ -4836,7 +4776,7 @@
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
-        <v>301</v>
+        <v>222</v>
       </c>
       <c r="C56" s="16">
         <v>0</v>
@@ -4844,7 +4784,7 @@
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="C57" s="17">
         <v>0</v>
@@ -4852,7 +4792,7 @@
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
-        <v>303</v>
+        <v>224</v>
       </c>
       <c r="C58" s="17">
         <v>0</v>
@@ -4860,7 +4800,7 @@
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
-        <v>304</v>
+        <v>225</v>
       </c>
       <c r="C59" s="17">
         <v>0</v>
@@ -4868,7 +4808,7 @@
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
-        <v>305</v>
+        <v>226</v>
       </c>
       <c r="C60" s="17">
         <v>0</v>
@@ -4876,7 +4816,7 @@
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
-        <v>306</v>
+        <v>227</v>
       </c>
       <c r="C61" s="17">
         <v>0</v>
@@ -4884,7 +4824,7 @@
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
-        <v>307</v>
+        <v>228</v>
       </c>
       <c r="C62" s="19">
         <v>2590</v>
@@ -4892,7 +4832,7 @@
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
-        <v>308</v>
+        <v>229</v>
       </c>
       <c r="C63" s="16">
         <v>0</v>
@@ -4900,7 +4840,7 @@
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
-        <v>309</v>
+        <v>230</v>
       </c>
       <c r="C64" s="16">
         <v>0</v>
@@ -4908,7 +4848,7 @@
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
-        <v>310</v>
+        <v>231</v>
       </c>
       <c r="C65" s="16">
         <v>0</v>
@@ -4916,7 +4856,7 @@
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
-        <v>311</v>
+        <v>232</v>
       </c>
       <c r="C66" s="16">
         <v>0</v>
@@ -4924,7 +4864,7 @@
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="C67" s="16">
         <v>0</v>
@@ -4932,7 +4872,7 @@
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
-        <v>313</v>
+        <v>234</v>
       </c>
       <c r="C68" s="16">
         <v>0</v>
@@ -4940,7 +4880,7 @@
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
-        <v>314</v>
+        <v>235</v>
       </c>
       <c r="C69" s="16">
         <v>0</v>
@@ -4948,7 +4888,7 @@
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="C70" s="16">
         <v>0</v>
@@ -4956,7 +4896,7 @@
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
-        <v>316</v>
+        <v>237</v>
       </c>
       <c r="C71" s="16">
         <v>0</v>
@@ -4964,7 +4904,7 @@
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
-        <v>317</v>
+        <v>238</v>
       </c>
       <c r="C72" s="16">
         <v>0</v>
@@ -4972,7 +4912,7 @@
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
-        <v>318</v>
+        <v>239</v>
       </c>
       <c r="C73" s="16">
         <v>0</v>
@@ -4980,7 +4920,7 @@
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
-        <v>319</v>
+        <v>240</v>
       </c>
       <c r="C74" s="16">
         <v>0</v>
@@ -4988,7 +4928,7 @@
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
-        <v>320</v>
+        <v>241</v>
       </c>
       <c r="C75" s="16">
         <v>0</v>
@@ -4996,7 +4936,7 @@
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
-        <v>321</v>
+        <v>242</v>
       </c>
       <c r="C76" s="16">
         <v>0</v>
@@ -5004,7 +4944,7 @@
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
-        <v>322</v>
+        <v>243</v>
       </c>
       <c r="C77" s="16">
         <v>0</v>
@@ -5012,7 +4952,7 @@
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
-        <v>323</v>
+        <v>244</v>
       </c>
       <c r="C78" s="16">
         <v>0</v>
@@ -5020,7 +4960,7 @@
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
-        <v>324</v>
+        <v>245</v>
       </c>
       <c r="C79" s="16">
         <v>0</v>
@@ -5028,7 +4968,7 @@
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
-        <v>325</v>
+        <v>246</v>
       </c>
       <c r="C80" s="16">
         <v>0</v>
@@ -5036,7 +4976,7 @@
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
-        <v>326</v>
+        <v>247</v>
       </c>
       <c r="C81" s="19">
         <v>5160</v>
@@ -5044,7 +4984,7 @@
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
-        <v>327</v>
+        <v>248</v>
       </c>
       <c r="C82" s="16">
         <v>0</v>
@@ -5052,7 +4992,7 @@
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
-        <v>328</v>
+        <v>249</v>
       </c>
       <c r="C83" s="16">
         <v>0</v>
@@ -5060,7 +5000,7 @@
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
-        <v>329</v>
+        <v>250</v>
       </c>
       <c r="C84" s="16">
         <v>0</v>
@@ -5068,7 +5008,7 @@
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
-        <v>330</v>
+        <v>251</v>
       </c>
       <c r="C85" s="16">
         <v>0</v>
@@ -5076,7 +5016,7 @@
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
-        <v>331</v>
+        <v>252</v>
       </c>
       <c r="C86" s="16">
         <v>0</v>
@@ -5084,7 +5024,7 @@
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
-        <v>332</v>
+        <v>253</v>
       </c>
       <c r="C87" s="16">
         <v>0</v>
@@ -5092,7 +5032,7 @@
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
-        <v>333</v>
+        <v>254</v>
       </c>
       <c r="C88" s="16">
         <v>0</v>
@@ -5100,7 +5040,7 @@
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
-        <v>334</v>
+        <v>255</v>
       </c>
       <c r="C89" s="16">
         <v>0</v>
@@ -5108,7 +5048,7 @@
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
-        <v>335</v>
+        <v>256</v>
       </c>
       <c r="C90" s="16">
         <v>0</v>
@@ -5116,7 +5056,7 @@
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
-        <v>336</v>
+        <v>257</v>
       </c>
       <c r="C91" s="16">
         <v>0</v>
@@ -5124,7 +5064,7 @@
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
-        <v>337</v>
+        <v>258</v>
       </c>
       <c r="C92" s="16">
         <v>0</v>
@@ -5132,7 +5072,7 @@
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
-        <v>338</v>
+        <v>259</v>
       </c>
       <c r="C93" s="16">
         <v>0</v>
@@ -5140,7 +5080,7 @@
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
-        <v>339</v>
+        <v>260</v>
       </c>
       <c r="C94" s="16">
         <v>0</v>
@@ -5148,7 +5088,7 @@
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
-        <v>340</v>
+        <v>261</v>
       </c>
       <c r="C95" s="16">
         <v>0</v>
@@ -5156,7 +5096,7 @@
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
-        <v>341</v>
+        <v>262</v>
       </c>
       <c r="C96" s="16">
         <v>0</v>
@@ -5164,7 +5104,7 @@
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
-        <v>342</v>
+        <v>263</v>
       </c>
       <c r="C97" s="16">
         <v>0</v>
@@ -5172,7 +5112,7 @@
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
-        <v>343</v>
+        <v>264</v>
       </c>
       <c r="C98" s="16">
         <v>0</v>
@@ -5180,7 +5120,7 @@
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
-        <v>344</v>
+        <v>265</v>
       </c>
       <c r="C99" s="16">
         <v>0</v>
@@ -5188,7 +5128,7 @@
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
-        <v>345</v>
+        <v>266</v>
       </c>
       <c r="C100" s="16">
         <v>0</v>
@@ -5196,7 +5136,7 @@
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
-        <v>346</v>
+        <v>267</v>
       </c>
       <c r="C101" s="16">
         <v>0</v>
@@ -5204,7 +5144,7 @@
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
-        <v>347</v>
+        <v>268</v>
       </c>
       <c r="C102" s="16">
         <v>0</v>
@@ -5212,7 +5152,7 @@
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
-        <v>348</v>
+        <v>269</v>
       </c>
       <c r="C103" s="16">
         <v>0</v>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF535F7-2D81-43BC-9153-FD974F402763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5DACDE-69BA-4CF0-947C-C1B4CFA32F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="HR" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="348">
   <si>
     <t>직급</t>
   </si>
@@ -1086,6 +1086,9 @@
   </si>
   <si>
     <t>plt</t>
+  </si>
+  <si>
+    <t>JFC WA</t>
   </si>
 </sst>
 </file>
@@ -1253,6 +1256,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1265,7 +1269,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -2421,17 +2424,33 @@
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="3"/>
+      <c r="B25" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E25" s="3">
+        <v>46251</v>
+      </c>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="3"/>
+      <c r="B26" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E26" s="3">
+        <v>46248</v>
+      </c>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4117,7 +4136,7 @@
       </c>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="28">
+      <c r="C8" s="24">
         <v>46023</v>
       </c>
       <c r="D8" s="10">
@@ -4128,7 +4147,7 @@
       </c>
     </row>
     <row r="9" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="28">
+      <c r="C9" s="24">
         <v>46054</v>
       </c>
       <c r="D9" s="10">
@@ -4139,7 +4158,7 @@
       </c>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C10" s="28">
+      <c r="C10" s="24">
         <v>46082</v>
       </c>
       <c r="D10" s="10">
@@ -4150,7 +4169,7 @@
       </c>
     </row>
     <row r="11" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="28">
+      <c r="C11" s="24">
         <v>46113</v>
       </c>
       <c r="D11" s="10">
@@ -4161,7 +4180,7 @@
       </c>
     </row>
     <row r="12" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="28">
+      <c r="C12" s="24">
         <v>46143</v>
       </c>
       <c r="D12" s="10">
@@ -4172,7 +4191,7 @@
       </c>
     </row>
     <row r="13" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C13" s="28">
+      <c r="C13" s="24">
         <v>46174</v>
       </c>
       <c r="D13" s="10">
@@ -4183,7 +4202,7 @@
       </c>
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="28">
+      <c r="C14" s="24">
         <v>46204</v>
       </c>
       <c r="D14" s="10">
@@ -4194,27 +4213,27 @@
       </c>
     </row>
     <row r="15" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C15" s="28">
+      <c r="C15" s="24">
         <v>46235</v>
       </c>
     </row>
     <row r="16" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="28">
+      <c r="C16" s="24">
         <v>46266</v>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" s="28">
+      <c r="C17" s="24">
         <v>46296</v>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C18" s="28">
+      <c r="C18" s="24">
         <v>46327</v>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C19" s="28">
+      <c r="C19" s="24">
         <v>46357</v>
       </c>
     </row>
@@ -4269,14 +4288,14 @@
       <c r="C5" s="16">
         <v>275</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="25" t="s">
         <v>336</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <f>SUM(C5:C35)</f>
         <v>4138</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="26">
         <f>SUM(C5:C21)/72+C35/45</f>
         <v>61.322222222222223</v>
       </c>
@@ -4296,9 +4315,9 @@
       <c r="C6" s="16">
         <v>248</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="7" t="s">
         <v>344</v>
       </c>
@@ -4379,14 +4398,14 @@
       <c r="C10" s="16">
         <v>318</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>C81</f>
         <v>5160</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="28">
         <f>F10/42</f>
         <v>122.85714285714286</v>
       </c>
@@ -4408,9 +4427,9 @@
       <c r="C11" s="16">
         <v>256</v>
       </c>
-      <c r="E11" s="24"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="27"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="7" t="s">
         <v>342</v>
       </c>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5DACDE-69BA-4CF0-947C-C1B4CFA32F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D91B9D-C08E-4953-B276-54EDF2CB8DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="HR" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="394">
   <si>
     <t>직급</t>
   </si>
@@ -58,15 +58,6 @@
     <t>구분</t>
   </si>
   <si>
-    <t>Purchasing, S&amp;R</t>
-  </si>
-  <si>
-    <t>S&amp;R</t>
-  </si>
-  <si>
-    <t>S&amp;R, Production</t>
-  </si>
-  <si>
     <t>True West Beef</t>
   </si>
   <si>
@@ -506,18 +497,6 @@
   </si>
   <si>
     <t>1 FTL</t>
-  </si>
-  <si>
-    <t>Lyons, Robert W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gonzalez Dieguez, Rolando </t>
-  </si>
-  <si>
-    <t>Garcia Gutierrez, Josue</t>
-  </si>
-  <si>
-    <t>Matthew(Insang) Joung</t>
   </si>
   <si>
     <t>Remond</t>
@@ -857,12 +836,6 @@
     <t>PK 홍합미역국</t>
   </si>
   <si>
-    <t>OFF</t>
-  </si>
-  <si>
-    <t>On</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -1089,6 +1062,171 @@
   </si>
   <si>
     <t>JFC WA</t>
+  </si>
+  <si>
+    <t>Ana Garcia Hortiz</t>
+  </si>
+  <si>
+    <t>Beatriz Rosales Cruz</t>
+  </si>
+  <si>
+    <t>Carmen Duarte</t>
+  </si>
+  <si>
+    <t>Cleotilde Hernandez Ramirez</t>
+  </si>
+  <si>
+    <t>Concepcion Garcia</t>
+  </si>
+  <si>
+    <t>Concepcion Ginez</t>
+  </si>
+  <si>
+    <t>Cynthia Rosales</t>
+  </si>
+  <si>
+    <t>Diane Gomez Rios</t>
+  </si>
+  <si>
+    <t>Dorotea Carolina Sanchez</t>
+  </si>
+  <si>
+    <t>Dulce Maria Garcia Martinez</t>
+  </si>
+  <si>
+    <t>Eliseo Garcia Entzana</t>
+  </si>
+  <si>
+    <t>Erika Contreras</t>
+  </si>
+  <si>
+    <t>Esmeralda Hernandez Santos</t>
+  </si>
+  <si>
+    <t>Evelia Garcia Martinez</t>
+  </si>
+  <si>
+    <t>Fernanda Barrancas</t>
+  </si>
+  <si>
+    <t>Floriberta Razcon Tlehuactle</t>
+  </si>
+  <si>
+    <t>Frausto Canchola</t>
+  </si>
+  <si>
+    <t>Gloria Martha Gonzales Cortes</t>
+  </si>
+  <si>
+    <t>Gredel Flores Villa</t>
+  </si>
+  <si>
+    <t>Gricelda Martinez</t>
+  </si>
+  <si>
+    <t>Guadalupe Contreras</t>
+  </si>
+  <si>
+    <t>Isidoro Hernandez</t>
+  </si>
+  <si>
+    <t>Ismael Villafana Hernandez</t>
+  </si>
+  <si>
+    <t>Itzel Cortez</t>
+  </si>
+  <si>
+    <t>Jocelyn Cervantes Bernal</t>
+  </si>
+  <si>
+    <t>Jorge Frutos</t>
+  </si>
+  <si>
+    <t>Josefa Diaz</t>
+  </si>
+  <si>
+    <t>Josue Garcia</t>
+  </si>
+  <si>
+    <t>Karen Carmona</t>
+  </si>
+  <si>
+    <t>Leonardo Rodriguez</t>
+  </si>
+  <si>
+    <t>Ma Teresa Macias Orozco</t>
+  </si>
+  <si>
+    <t>Margarita Garcia</t>
+  </si>
+  <si>
+    <t>Maria Carmona</t>
+  </si>
+  <si>
+    <t>Maria De Los Angeles Villazana</t>
+  </si>
+  <si>
+    <t>Maria Garcia</t>
+  </si>
+  <si>
+    <t>Maria Hernandez Rangel</t>
+  </si>
+  <si>
+    <t>Maria Janeth Villa</t>
+  </si>
+  <si>
+    <t>Maria Villasenor</t>
+  </si>
+  <si>
+    <t>Maria Nelva Guererro Murillo</t>
+  </si>
+  <si>
+    <t>Olga Carmona</t>
+  </si>
+  <si>
+    <t>Patricia Molohua</t>
+  </si>
+  <si>
+    <t>Rey Perez Martinez</t>
+  </si>
+  <si>
+    <t>Meuy Chan</t>
+  </si>
+  <si>
+    <t>Robert W Lyons</t>
+  </si>
+  <si>
+    <t>Rodrigo Avila</t>
+  </si>
+  <si>
+    <t>Rolando Gonzalez Dieguez</t>
+  </si>
+  <si>
+    <t>Shulami Rios Ramirez</t>
+  </si>
+  <si>
+    <t>Sofia Lopez</t>
+  </si>
+  <si>
+    <t>Silvia Pompa Perez</t>
+  </si>
+  <si>
+    <t>Uriel Adalberto Rodriguez Gonzalez</t>
+  </si>
+  <si>
+    <t>Yuridia Salgado</t>
+  </si>
+  <si>
+    <t>On Time</t>
+  </si>
+  <si>
+    <t>Vacation</t>
+  </si>
+  <si>
+    <t>Late; no call</t>
+  </si>
+  <si>
+    <t>Pregnant</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1238,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1141,13 +1279,37 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF753800"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -1195,7 +1357,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1268,6 +1430,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1606,7 +1780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D083C086-594E-4C2B-9782-7E24033B84D9}">
-  <dimension ref="B1:H6"/>
+  <dimension ref="B2:H53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -1617,91 +1791,695 @@
     <col min="8" max="8" width="50.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="2:8" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="2" t="s">
-        <v>276</v>
-      </c>
+      <c r="H2" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="29" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B6" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="29" t="s">
+        <v>343</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B11" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B12" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B15" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="29" t="s">
+        <v>353</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B18" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B20" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="29" t="s">
+        <v>357</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="29" t="s">
+        <v>360</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B25" s="29" t="s">
+        <v>361</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="29" t="s">
+        <v>363</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B30" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B33" s="29" t="s">
+        <v>369</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="29" t="s">
+        <v>370</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="29" t="s">
+        <v>371</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+    </row>
+    <row r="36" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B36" s="29" t="s">
+        <v>372</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="29" t="s">
+        <v>374</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="29" t="s">
+        <v>376</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B41" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="29" t="s">
+        <v>378</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="29" t="s">
+        <v>380</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B45" s="29" t="s">
+        <v>381</v>
+      </c>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46" s="29" t="s">
+        <v>382</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="29" t="s">
+        <v>383</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+    </row>
+    <row r="48" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B48" s="29" t="s">
+        <v>384</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="29" t="s">
+        <v>385</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="29" t="s">
+        <v>386</v>
+      </c>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+    </row>
+    <row r="52" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
+      <c r="B52" s="29" t="s">
+        <v>388</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1725,51 +2503,51 @@
   <sheetData>
     <row r="2" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>302</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="I3" s="6">
         <v>46249</v>
@@ -1777,25 +2555,25 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I4" s="6">
         <v>46254</v>
@@ -1803,25 +2581,25 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="I5" s="6">
         <v>46258</v>
@@ -1829,25 +2607,25 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="I6" s="6">
         <v>46254</v>
@@ -1855,25 +2633,25 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="I7" s="6">
         <v>46254</v>
@@ -1881,25 +2659,25 @@
     </row>
     <row r="8" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>286</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="I8" s="6">
         <v>46251</v>
@@ -1907,25 +2685,25 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="G9" s="5" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="I9" s="6">
         <v>46254</v>
@@ -1933,25 +2711,25 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="I10" s="6">
         <v>46258</v>
@@ -1959,25 +2737,25 @@
     </row>
     <row r="11" spans="2:9" ht="42.75" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="I11" s="6">
         <v>46260</v>
@@ -1985,25 +2763,25 @@
     </row>
     <row r="12" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="I12" s="6">
         <v>46249</v>
@@ -2011,22 +2789,22 @@
     </row>
     <row r="13" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="H13" s="6">
         <v>46262</v>
@@ -2054,30 +2832,30 @@
     <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E3" s="3">
         <v>46217</v>
@@ -2086,81 +2864,81 @@
     </row>
     <row r="4" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E4" s="3">
         <v>46218</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E5" s="3">
         <v>46223</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E6" s="3">
         <v>46225</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E7" s="3">
         <v>46226</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E8" s="3">
         <v>46232</v>
@@ -2169,47 +2947,47 @@
     </row>
     <row r="9" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E9" s="3">
         <v>46234</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E10" s="3">
         <v>46237</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E11" s="3">
         <v>46223</v>
@@ -2218,13 +2996,13 @@
     </row>
     <row r="12" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E12" s="3">
         <v>46223</v>
@@ -2233,30 +3011,30 @@
     </row>
     <row r="13" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E13" s="3">
         <v>46238</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E14" s="3">
         <v>46239</v>
@@ -2265,13 +3043,13 @@
     </row>
     <row r="15" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E15" s="3">
         <v>46241</v>
@@ -2280,64 +3058,64 @@
     </row>
     <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E16" s="3">
         <v>46245</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E17" s="3">
         <v>46251</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E18" s="3">
         <v>46251</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E19" s="3">
         <v>46253</v>
@@ -2346,30 +3124,30 @@
     </row>
     <row r="20" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E20" s="3">
         <v>46258</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E21" s="3">
         <v>46251</v>
@@ -2378,13 +3156,13 @@
     </row>
     <row r="22" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E22" s="3">
         <v>46261</v>
@@ -2393,30 +3171,30 @@
     </row>
     <row r="23" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E23" s="3">
         <v>46252</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E24" s="3">
         <v>46245</v>
@@ -2425,13 +3203,13 @@
     </row>
     <row r="25" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E25" s="3">
         <v>46251</v>
@@ -2440,13 +3218,13 @@
     </row>
     <row r="26" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E26" s="3">
         <v>46248</v>
@@ -2514,25 +3292,25 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C3" s="8">
         <v>4.13</v>
       </c>
       <c r="D3" s="8"/>
       <c r="G3" s="11" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="H3" s="12">
         <v>4.4000000000000004</v>
@@ -2540,14 +3318,14 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4" s="8">
         <v>4.1099999999999994</v>
       </c>
       <c r="D4" s="8"/>
       <c r="G4" s="11" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="H4" s="12">
         <f>AVERAGE(D3:D155)</f>
@@ -2556,7 +3334,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="8">
         <v>4.1999999999999993</v>
@@ -2565,7 +3343,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="H5" s="13">
         <f>(H4-H3)/H3</f>
@@ -2574,14 +3352,14 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C6" s="8">
         <v>4.2199999999999989</v>
       </c>
       <c r="D6" s="8"/>
       <c r="G6" s="11" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="H6" s="11" t="str">
         <f>COUNT(D3:D370)&amp;"FTL"</f>
@@ -2590,7 +3368,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C7" s="8">
         <v>4.1599999999999993</v>
@@ -2599,7 +3377,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" s="8">
         <v>4.2399999999999993</v>
@@ -2608,7 +3386,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9" s="8">
         <v>4.2799999999999994</v>
@@ -2617,7 +3395,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C10" s="8">
         <v>4.2399999999999993</v>
@@ -2628,7 +3406,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11" s="8">
         <v>4.1999999999999993</v>
@@ -2637,7 +3415,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" s="8">
         <v>4.2299999999999995</v>
@@ -2648,7 +3426,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C13" s="8">
         <v>4.1599999999999993</v>
@@ -2657,7 +3435,7 @@
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C14" s="8">
         <v>4.3099999999999996</v>
@@ -2666,7 +3444,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C15" s="8">
         <v>4.2399999999999993</v>
@@ -2677,7 +3455,7 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C16" s="8">
         <v>4.2799999999999994</v>
@@ -2686,7 +3464,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C17" s="8">
         <v>4.3299999999999992</v>
@@ -2695,7 +3473,7 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C18" s="8">
         <v>4.339999999999999</v>
@@ -2704,7 +3482,7 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C19" s="8">
         <v>4.3299999999999992</v>
@@ -2713,7 +3491,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C20" s="8">
         <v>4.2399999999999993</v>
@@ -2722,7 +3500,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C21" s="8">
         <v>4.2199999999999989</v>
@@ -2731,7 +3509,7 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C22" s="8">
         <v>4.2199999999999989</v>
@@ -2740,7 +3518,7 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C23" s="8">
         <v>4.2799999999999994</v>
@@ -2749,7 +3527,7 @@
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C24" s="8">
         <v>4.3299999999999992</v>
@@ -2760,7 +3538,7 @@
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C25" s="8">
         <v>4.3099999999999996</v>
@@ -2769,7 +3547,7 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C26" s="8">
         <v>4.2499999999999991</v>
@@ -2780,7 +3558,7 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C27" s="8">
         <v>4.2699999999999996</v>
@@ -2789,7 +3567,7 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C28" s="8">
         <v>4.2699999999999996</v>
@@ -2800,7 +3578,7 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C29" s="8">
         <v>4.3099999999999996</v>
@@ -2809,7 +3587,7 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C30" s="8">
         <v>4.2299999999999995</v>
@@ -2820,7 +3598,7 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C31" s="8">
         <v>4.2299999999999995</v>
@@ -2829,7 +3607,7 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C32" s="8">
         <v>4.18</v>
@@ -2840,7 +3618,7 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C33" s="8">
         <v>4.2599999999999989</v>
@@ -2849,7 +3627,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C34" s="8">
         <v>4.2699999999999996</v>
@@ -2858,7 +3636,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C35" s="8">
         <v>4.2599999999999989</v>
@@ -2867,7 +3645,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C36" s="8">
         <v>4.2399999999999993</v>
@@ -2878,7 +3656,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C37" s="8">
         <v>4.2899999999999991</v>
@@ -2887,7 +3665,7 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C38" s="8">
         <v>4.2899999999999991</v>
@@ -2896,7 +3674,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C39" s="8">
         <v>4.3099999999999996</v>
@@ -2905,7 +3683,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C40" s="8">
         <v>4.3899999999999997</v>
@@ -2916,7 +3694,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C41" s="8">
         <v>4.4099999999999993</v>
@@ -2925,7 +3703,7 @@
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C42" s="8">
         <v>4.419999999999999</v>
@@ -2936,7 +3714,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C43" s="8">
         <v>4.4499999999999993</v>
@@ -2945,7 +3723,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C44" s="8">
         <v>4.4699999999999989</v>
@@ -2954,7 +3732,7 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C45" s="8">
         <v>4.4799999999999995</v>
@@ -2963,7 +3741,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C46" s="8">
         <v>4.4899999999999993</v>
@@ -2972,7 +3750,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C47" s="8">
         <v>4.669999999999999</v>
@@ -2983,7 +3761,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C48" s="8">
         <v>4.5799999999999992</v>
@@ -2992,7 +3770,7 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C49" s="8">
         <v>4.669999999999999</v>
@@ -3001,7 +3779,7 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C50" s="8">
         <v>4.5699999999999994</v>
@@ -3012,7 +3790,7 @@
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C51" s="8">
         <v>4.589999999999999</v>
@@ -3021,7 +3799,7 @@
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C52" s="8">
         <v>4.5499999999999989</v>
@@ -3032,7 +3810,7 @@
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C53" s="8">
         <v>4.7199999999999989</v>
@@ -3041,7 +3819,7 @@
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B54" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C54" s="8">
         <v>4.6399999999999997</v>
@@ -3050,7 +3828,7 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C55" s="8">
         <v>4.6499999999999995</v>
@@ -3061,7 +3839,7 @@
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C56" s="8">
         <v>4.6399999999999997</v>
@@ -3070,7 +3848,7 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C57" s="8">
         <v>4.6099999999999994</v>
@@ -3081,7 +3859,7 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C58" s="8">
         <v>4.5299999999999994</v>
@@ -3092,7 +3870,7 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C59" s="8">
         <v>4.6599999999999993</v>
@@ -3101,7 +3879,7 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C60" s="8">
         <v>4.4999999999999991</v>
@@ -3110,7 +3888,7 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C61" s="8">
         <v>4.5599999999999996</v>
@@ -3119,7 +3897,7 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C62" s="8">
         <v>4.5299999999999994</v>
@@ -3130,7 +3908,7 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C63" s="8">
         <v>4.5099999999999989</v>
@@ -3139,7 +3917,7 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C64" s="8">
         <v>4.5499999999999989</v>
@@ -3148,7 +3926,7 @@
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C65" s="8">
         <v>4.5099999999999989</v>
@@ -3157,7 +3935,7 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C66" s="8">
         <v>4.4599999999999991</v>
@@ -3166,7 +3944,7 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C67" s="8">
         <v>4.4499999999999993</v>
@@ -3175,7 +3953,7 @@
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C68" s="8">
         <v>4.4499999999999993</v>
@@ -3186,7 +3964,7 @@
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C69" s="8">
         <v>4.3999999999999995</v>
@@ -3195,7 +3973,7 @@
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C70" s="8">
         <v>4.3599999999999994</v>
@@ -3204,7 +3982,7 @@
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C71" s="8">
         <v>4.3599999999999994</v>
@@ -3215,7 +3993,7 @@
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C72" s="8">
         <v>4.2599999999999989</v>
@@ -3224,7 +4002,7 @@
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C73" s="8">
         <v>4.2299999999999995</v>
@@ -3235,7 +4013,7 @@
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C74" s="8">
         <v>4.2499999999999991</v>
@@ -3244,7 +4022,7 @@
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C75" s="8">
         <v>4.2199999999999989</v>
@@ -3253,7 +4031,7 @@
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C76" s="8">
         <v>4.2499999999999991</v>
@@ -3264,7 +4042,7 @@
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C77" s="8">
         <v>4.2599999999999989</v>
@@ -3273,7 +4051,7 @@
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C78" s="8">
         <v>4.2699999999999996</v>
@@ -3284,7 +4062,7 @@
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C79" s="8">
         <v>4.17</v>
@@ -3293,7 +4071,7 @@
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C80" s="8">
         <v>4.2399999999999993</v>
@@ -3302,7 +4080,7 @@
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C81" s="8">
         <v>4.2399999999999993</v>
@@ -3313,7 +4091,7 @@
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C82" s="8">
         <v>4.2499999999999991</v>
@@ -3322,7 +4100,7 @@
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C83" s="8">
         <v>4.2799999999999994</v>
@@ -3333,7 +4111,7 @@
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C84" s="8">
         <v>4.3099999999999996</v>
@@ -3342,7 +4120,7 @@
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C85" s="8">
         <v>4.2899999999999991</v>
@@ -3351,7 +4129,7 @@
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C86" s="8">
         <v>4.3199999999999994</v>
@@ -3362,7 +4140,7 @@
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C87" s="8">
         <v>4.419999999999999</v>
@@ -3371,7 +4149,7 @@
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C88" s="8">
         <v>4.3699999999999992</v>
@@ -3382,7 +4160,7 @@
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C89" s="8">
         <v>4.3699999999999992</v>
@@ -3391,7 +4169,7 @@
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C90" s="8">
         <v>4.379999999999999</v>
@@ -3400,7 +4178,7 @@
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C91" s="8">
         <v>4.3899999999999997</v>
@@ -3409,7 +4187,7 @@
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C92" s="8">
         <v>4.43</v>
@@ -3418,7 +4196,7 @@
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C93" s="8">
         <v>4.3099999999999996</v>
@@ -3429,7 +4207,7 @@
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B94" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C94" s="8">
         <v>4.3899999999999997</v>
@@ -3438,7 +4216,7 @@
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B95" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C95" s="8">
         <v>4.4399999999999995</v>
@@ -3447,7 +4225,7 @@
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B96" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C96" s="8">
         <v>4.3999999999999995</v>
@@ -3456,7 +4234,7 @@
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C97" s="8">
         <v>4.4399999999999995</v>
@@ -3465,7 +4243,7 @@
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C98" s="8">
         <v>4.379999999999999</v>
@@ -3476,7 +4254,7 @@
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C99" s="8">
         <v>4.4599999999999991</v>
@@ -3485,7 +4263,7 @@
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C100" s="8">
         <v>4.419999999999999</v>
@@ -3494,7 +4272,7 @@
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C101" s="8">
         <v>4.5199999999999996</v>
@@ -3505,7 +4283,7 @@
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C102" s="8">
         <v>4.4399999999999995</v>
@@ -3514,7 +4292,7 @@
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C103" s="8">
         <v>4.5399999999999991</v>
@@ -3523,7 +4301,7 @@
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C104" s="8">
         <v>4.4799999999999995</v>
@@ -3532,7 +4310,7 @@
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C105" s="8">
         <v>4.5299999999999994</v>
@@ -3543,7 +4321,7 @@
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C106" s="8">
         <v>4.4899999999999993</v>
@@ -3552,7 +4330,7 @@
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C107" s="8">
         <v>4.4999999999999991</v>
@@ -3563,7 +4341,7 @@
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C108" s="8">
         <v>4.5799999999999992</v>
@@ -3572,7 +4350,7 @@
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C109" s="8">
         <v>4.5699999999999994</v>
@@ -3581,7 +4359,7 @@
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C110" s="8">
         <v>4.4699999999999989</v>
@@ -3592,7 +4370,7 @@
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C111" s="8">
         <v>4.379999999999999</v>
@@ -3601,7 +4379,7 @@
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C112" s="8">
         <v>4.589999999999999</v>
@@ -3612,7 +4390,7 @@
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C113" s="8">
         <v>4.6399999999999997</v>
@@ -3621,7 +4399,7 @@
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C114" s="8">
         <v>4.5099999999999989</v>
@@ -3630,7 +4408,7 @@
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C115" s="8">
         <v>4.5299999999999994</v>
@@ -3639,7 +4417,7 @@
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C116" s="8">
         <v>4.5599999999999996</v>
@@ -3648,7 +4426,7 @@
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C117" s="8">
         <v>4.6499999999999995</v>
@@ -3657,7 +4435,7 @@
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C118" s="8">
         <v>4.5599999999999996</v>
@@ -3666,7 +4444,7 @@
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B119" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C119" s="8">
         <v>4.6499999999999995</v>
@@ -3677,7 +4455,7 @@
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C120" s="8">
         <v>4.5999999999999996</v>
@@ -3686,7 +4464,7 @@
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B121" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C121" s="8">
         <v>4.6099999999999994</v>
@@ -3695,7 +4473,7 @@
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B122" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C122" s="8">
         <v>4.6599999999999993</v>
@@ -3704,7 +4482,7 @@
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B123" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C123" s="8">
         <v>4.5999999999999996</v>
@@ -3715,7 +4493,7 @@
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C124" s="8">
         <v>4.629999999999999</v>
@@ -3724,7 +4502,7 @@
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B125" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C125" s="8">
         <v>4.6099999999999994</v>
@@ -3733,7 +4511,7 @@
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C126" s="8">
         <v>4.669999999999999</v>
@@ -3742,7 +4520,7 @@
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B127" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C127" s="8">
         <v>4.5599999999999996</v>
@@ -4081,15 +4859,15 @@
     <row r="3" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C3" s="7"/>
       <c r="D3" s="7" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C4" s="7" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="D4" s="8">
         <v>15520853.789999999</v>
@@ -4100,7 +4878,7 @@
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C5" s="7" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D5" s="8">
         <f>D4/12</f>
@@ -4113,7 +4891,7 @@
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C6" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="D6" s="8">
         <v>8817263.6600000001</v>
@@ -4124,7 +4902,7 @@
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C7" s="7" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D7" s="8">
         <f>D6/7</f>
@@ -4258,7 +5036,7 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="26.25" x14ac:dyDescent="0.25">
@@ -4266,30 +5044,30 @@
         <v>3</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E4" s="20"/>
       <c r="F4" s="20" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="15" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C5" s="16">
         <v>275</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F5" s="26">
         <f>SUM(C5:C35)</f>
@@ -4300,7 +5078,7 @@
         <v>61.322222222222223</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="I5" s="7">
         <f>COUNTIF(C5:C15,"&lt;100")+COUNTIF(C20:C21,"&lt;100")</f>
@@ -4310,7 +5088,7 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C6" s="16">
         <v>248</v>
@@ -4319,7 +5097,7 @@
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
       <c r="H6" s="7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="I6" s="7">
         <f>COUNTIF(C5:C15,"&gt;300")+COUNTIF(C20:C21,"&gt;300")</f>
@@ -4329,13 +5107,13 @@
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C7" s="16">
         <v>370</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="F7" s="20">
         <v>0</v>
@@ -4349,13 +5127,13 @@
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C8" s="16">
         <v>258</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="F8" s="20">
         <f>SUM(C49:C56)</f>
@@ -4371,13 +5149,13 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="15" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C9" s="16">
         <v>283</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="F9" s="22">
         <f>C62</f>
@@ -4393,13 +5171,13 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C10" s="16">
         <v>318</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="F10" s="27">
         <f>C81</f>
@@ -4410,19 +5188,19 @@
         <v>122.85714285714286</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="I10" s="23">
         <f>39296/42/24</f>
         <v>38.984126984126981</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="15" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C11" s="16">
         <v>256</v>
@@ -4431,19 +5209,19 @@
       <c r="F11" s="27"/>
       <c r="G11" s="28"/>
       <c r="H11" s="7" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="I11" s="7">
         <f>84672/42/24</f>
         <v>84</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C12" s="16">
         <v>241</v>
@@ -4451,7 +5229,7 @@
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="15" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C13" s="16">
         <v>201</v>
@@ -4459,7 +5237,7 @@
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C14" s="16">
         <v>256</v>
@@ -4467,7 +5245,7 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C15" s="16">
         <v>269</v>
@@ -4475,7 +5253,7 @@
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C16" s="16">
         <v>0</v>
@@ -4483,7 +5261,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C17" s="16">
         <v>0</v>
@@ -4491,7 +5269,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C18" s="16">
         <v>0</v>
@@ -4499,7 +5277,7 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C19" s="16">
         <v>0</v>
@@ -4507,7 +5285,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C20" s="16">
         <v>322</v>
@@ -4515,7 +5293,7 @@
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C21" s="16">
         <v>379</v>
@@ -4523,7 +5301,7 @@
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C22" s="16">
         <v>0</v>
@@ -4531,7 +5309,7 @@
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C23" s="16">
         <v>0</v>
@@ -4539,7 +5317,7 @@
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C24" s="16">
         <v>0</v>
@@ -4547,7 +5325,7 @@
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C25" s="16">
         <v>0</v>
@@ -4555,7 +5333,7 @@
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C26" s="16">
         <v>0</v>
@@ -4563,7 +5341,7 @@
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C27" s="16">
         <v>0</v>
@@ -4571,7 +5349,7 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C28" s="16">
         <v>0</v>
@@ -4579,7 +5357,7 @@
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C29" s="16">
         <v>0</v>
@@ -4587,7 +5365,7 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C30" s="16">
         <v>0</v>
@@ -4595,7 +5373,7 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C31" s="16">
         <v>0</v>
@@ -4603,7 +5381,7 @@
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C32" s="16">
         <v>0</v>
@@ -4611,7 +5389,7 @@
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C33" s="16">
         <v>0</v>
@@ -4619,7 +5397,7 @@
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C34" s="16">
         <v>0</v>
@@ -4627,7 +5405,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C35" s="16">
         <v>462</v>
@@ -4635,7 +5413,7 @@
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C36" s="16">
         <v>0</v>
@@ -4643,7 +5421,7 @@
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C37" s="16">
         <v>0</v>
@@ -4651,7 +5429,7 @@
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C38" s="17">
         <v>0</v>
@@ -4659,7 +5437,7 @@
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C39" s="16">
         <v>0</v>
@@ -4667,7 +5445,7 @@
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C40" s="17">
         <v>0</v>
@@ -4675,7 +5453,7 @@
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C41" s="17">
         <v>0</v>
@@ -4683,7 +5461,7 @@
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C42" s="17">
         <v>0</v>
@@ -4691,7 +5469,7 @@
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C43" s="17">
         <v>0</v>
@@ -4699,7 +5477,7 @@
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C44" s="16">
         <v>0</v>
@@ -4707,7 +5485,7 @@
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C45" s="16">
         <v>0</v>
@@ -4715,7 +5493,7 @@
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C46" s="16">
         <v>0</v>
@@ -4723,7 +5501,7 @@
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C47" s="16">
         <v>0</v>
@@ -4731,7 +5509,7 @@
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" s="18" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C48" s="16">
         <v>0</v>
@@ -4739,7 +5517,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C49" s="16">
         <v>0</v>
@@ -4747,7 +5525,7 @@
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C50" s="16">
         <v>0</v>
@@ -4755,7 +5533,7 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C51" s="17">
         <v>78</v>
@@ -4763,7 +5541,7 @@
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C52" s="16">
         <v>0</v>
@@ -4771,7 +5549,7 @@
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C53" s="16">
         <v>0</v>
@@ -4779,7 +5557,7 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C54" s="16">
         <v>160</v>
@@ -4787,7 +5565,7 @@
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C55" s="16">
         <v>191</v>
@@ -4795,7 +5573,7 @@
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C56" s="16">
         <v>0</v>
@@ -4803,7 +5581,7 @@
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C57" s="17">
         <v>0</v>
@@ -4811,7 +5589,7 @@
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C58" s="17">
         <v>0</v>
@@ -4819,7 +5597,7 @@
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C59" s="17">
         <v>0</v>
@@ -4827,7 +5605,7 @@
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C60" s="17">
         <v>0</v>
@@ -4835,7 +5613,7 @@
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C61" s="17">
         <v>0</v>
@@ -4843,7 +5621,7 @@
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C62" s="19">
         <v>2590</v>
@@ -4851,7 +5629,7 @@
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C63" s="16">
         <v>0</v>
@@ -4859,7 +5637,7 @@
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C64" s="16">
         <v>0</v>
@@ -4867,7 +5645,7 @@
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C65" s="16">
         <v>0</v>
@@ -4875,7 +5653,7 @@
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C66" s="16">
         <v>0</v>
@@ -4883,7 +5661,7 @@
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C67" s="16">
         <v>0</v>
@@ -4891,7 +5669,7 @@
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C68" s="16">
         <v>0</v>
@@ -4899,7 +5677,7 @@
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C69" s="16">
         <v>0</v>
@@ -4907,7 +5685,7 @@
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C70" s="16">
         <v>0</v>
@@ -4915,7 +5693,7 @@
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C71" s="16">
         <v>0</v>
@@ -4923,7 +5701,7 @@
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C72" s="16">
         <v>0</v>
@@ -4931,7 +5709,7 @@
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C73" s="16">
         <v>0</v>
@@ -4939,7 +5717,7 @@
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C74" s="16">
         <v>0</v>
@@ -4947,7 +5725,7 @@
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C75" s="16">
         <v>0</v>
@@ -4955,7 +5733,7 @@
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C76" s="16">
         <v>0</v>
@@ -4963,7 +5741,7 @@
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C77" s="16">
         <v>0</v>
@@ -4971,7 +5749,7 @@
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C78" s="16">
         <v>0</v>
@@ -4979,7 +5757,7 @@
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C79" s="16">
         <v>0</v>
@@ -4987,7 +5765,7 @@
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C80" s="16">
         <v>0</v>
@@ -4995,7 +5773,7 @@
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C81" s="19">
         <v>5160</v>
@@ -5003,7 +5781,7 @@
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C82" s="16">
         <v>0</v>
@@ -5011,7 +5789,7 @@
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C83" s="16">
         <v>0</v>
@@ -5019,7 +5797,7 @@
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C84" s="16">
         <v>0</v>
@@ -5027,7 +5805,7 @@
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C85" s="16">
         <v>0</v>
@@ -5035,7 +5813,7 @@
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C86" s="16">
         <v>0</v>
@@ -5043,7 +5821,7 @@
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C87" s="16">
         <v>0</v>
@@ -5051,7 +5829,7 @@
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C88" s="16">
         <v>0</v>
@@ -5059,7 +5837,7 @@
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C89" s="16">
         <v>0</v>
@@ -5067,7 +5845,7 @@
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C90" s="16">
         <v>0</v>
@@ -5075,7 +5853,7 @@
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C91" s="16">
         <v>0</v>
@@ -5083,7 +5861,7 @@
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C92" s="16">
         <v>0</v>
@@ -5091,7 +5869,7 @@
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C93" s="16">
         <v>0</v>
@@ -5099,7 +5877,7 @@
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C94" s="16">
         <v>0</v>
@@ -5107,7 +5885,7 @@
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C95" s="16">
         <v>0</v>
@@ -5115,7 +5893,7 @@
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C96" s="16">
         <v>0</v>
@@ -5123,7 +5901,7 @@
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C97" s="16">
         <v>0</v>
@@ -5131,7 +5909,7 @@
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C98" s="16">
         <v>0</v>
@@ -5139,7 +5917,7 @@
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C99" s="16">
         <v>0</v>
@@ -5147,7 +5925,7 @@
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C100" s="16">
         <v>0</v>
@@ -5155,7 +5933,7 @@
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C101" s="16">
         <v>0</v>
@@ -5163,7 +5941,7 @@
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C102" s="16">
         <v>0</v>
@@ -5171,7 +5949,7 @@
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C103" s="16">
         <v>0</v>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D91B9D-C08E-4953-B276-54EDF2CB8DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95281F31-0DAD-40DB-B0D9-27EAD8D4FED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="HR" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="394">
   <si>
     <t>직급</t>
   </si>
@@ -1223,10 +1223,10 @@
     <t>Vacation</t>
   </si>
   <si>
-    <t>Late; no call</t>
-  </si>
-  <si>
     <t>Pregnant</t>
+  </si>
+  <si>
+    <t>Off (fill form)</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1238,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1297,6 +1297,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF5A3286"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1312,7 +1318,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1350,6 +1356,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1357,7 +1393,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1419,6 +1455,12 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1431,16 +1473,19 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1791,7 +1836,7 @@
     <col min="8" max="8" width="50.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>263</v>
       </c>
@@ -1814,574 +1859,570 @@
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="29" t="s">
+    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="25" t="s">
         <v>339</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="31" t="s">
         <v>390</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="29" t="s">
+    <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="25" t="s">
         <v>340</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="25" t="s">
         <v>341</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B6" s="29" t="s">
+    <row r="6" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="25" t="s">
         <v>342</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="29" t="s">
+    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="25" t="s">
         <v>343</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="29" t="s">
+    <row r="8" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="25" t="s">
         <v>344</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="29" t="s">
+    <row r="9" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="25" t="s">
         <v>345</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="29" t="s">
+    <row r="10" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="25" t="s">
         <v>346</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="30" t="s">
-        <v>390</v>
+      <c r="E10" s="33" t="s">
+        <v>393</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B11" s="29" t="s">
+    <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="25" t="s">
         <v>347</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B12" s="29" t="s">
+    <row r="12" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="25" t="s">
         <v>348</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="34" t="s">
         <v>391</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="29" t="s">
+    <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="25" t="s">
         <v>349</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="30" t="s">
-        <v>390</v>
-      </c>
+      <c r="E13" s="35"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="29" t="s">
+    <row r="14" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="25" t="s">
         <v>350</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B15" s="29" t="s">
+    <row r="15" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="25" t="s">
         <v>351</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="32"/>
+      <c r="E15" s="32" t="s">
+        <v>390</v>
+      </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="29" t="s">
+    <row r="16" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="25" t="s">
         <v>352</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="29" t="s">
+    <row r="17" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="25" t="s">
         <v>353</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B18" s="29" t="s">
+    <row r="18" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="25" t="s">
         <v>354</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="29" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="25" t="s">
         <v>355</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B20" s="29" t="s">
+    <row r="20" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="25" t="s">
         <v>356</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="29" t="s">
+    <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="25" t="s">
         <v>357</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="30" t="s">
+      <c r="E21" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="29" t="s">
+    <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="25" t="s">
         <v>358</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="29" t="s">
+    <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="25" t="s">
         <v>359</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="30" t="s">
+      <c r="E23" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="29" t="s">
+    <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="25" t="s">
         <v>360</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B25" s="29" t="s">
+    <row r="25" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="25" t="s">
         <v>361</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="30" t="s">
+      <c r="E25" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="29" t="s">
+    <row r="26" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="25" t="s">
         <v>362</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="30" t="s">
-        <v>390</v>
-      </c>
+      <c r="E26" s="35"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="29" t="s">
+    <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="25" t="s">
         <v>363</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
-      <c r="E27" s="32"/>
+      <c r="E27" s="35"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="29" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="25" t="s">
         <v>364</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="32"/>
+      <c r="E28" s="32" t="s">
+        <v>390</v>
+      </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="29" t="s">
+    <row r="29" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="25" t="s">
         <v>365</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
-      <c r="E29" s="30" t="s">
+      <c r="E29" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B30" s="29" t="s">
+    <row r="30" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="25" t="s">
         <v>366</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
-      <c r="E30" s="30" t="s">
-        <v>392</v>
+      <c r="E30" s="32" t="s">
+        <v>390</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="29" t="s">
+    <row r="31" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="25" t="s">
         <v>367</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
-      <c r="E31" s="30" t="s">
-        <v>390</v>
+      <c r="E31" s="34" t="s">
+        <v>391</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="29" t="s">
+    <row r="32" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="25" t="s">
         <v>368</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="31" t="s">
-        <v>391</v>
+      <c r="E32" s="32" t="s">
+        <v>390</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B33" s="29" t="s">
+    <row r="33" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="25" t="s">
         <v>369</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
-      <c r="E33" s="30" t="s">
+      <c r="E33" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="29" t="s">
+    <row r="34" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="25" t="s">
         <v>370</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="30" t="s">
+      <c r="E34" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="29" t="s">
+    <row r="35" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="25" t="s">
         <v>371</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="30" t="s">
+      <c r="E35" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B36" s="29" t="s">
+    <row r="36" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="25" t="s">
         <v>372</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="30" t="s">
+      <c r="E36" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="29" t="s">
+    <row r="37" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="25" t="s">
         <v>373</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="30" t="s">
+      <c r="E37" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="29" t="s">
+    <row r="38" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="25" t="s">
         <v>374</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="30" t="s">
+      <c r="E38" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="29" t="s">
+    <row r="39" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="25" t="s">
         <v>375</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="30" t="s">
+      <c r="E39" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="29" t="s">
+    <row r="40" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="25" t="s">
         <v>376</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="30" t="s">
+      <c r="E40" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B41" s="29" t="s">
+    <row r="41" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="25" t="s">
         <v>377</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="30" t="s">
+      <c r="E41" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="29" t="s">
+    <row r="42" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="25" t="s">
         <v>378</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="29" t="s">
+    <row r="43" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="25" t="s">
         <v>379</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="30" t="s">
-        <v>390</v>
-      </c>
+      <c r="E43" s="35"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="29" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="25" t="s">
         <v>380</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="30" t="s">
-        <v>390</v>
-      </c>
+      <c r="E44" s="35"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="29" t="s">
+    <row r="45" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="25" t="s">
         <v>381</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="30" t="s">
+      <c r="E45" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="29" t="s">
+    <row r="46" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="25" t="s">
         <v>382</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="30" t="s">
+      <c r="E46" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F46" s="7"/>
@@ -2390,78 +2431,78 @@
         <v>267</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="29" t="s">
+    <row r="47" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="25" t="s">
         <v>383</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="30" t="s">
+      <c r="E47" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B48" s="29" t="s">
+    <row r="48" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="25" t="s">
         <v>384</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="30" t="s">
+      <c r="E48" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="29" t="s">
+    <row r="49" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="25" t="s">
         <v>385</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
-      <c r="E49" s="30" t="s">
-        <v>390</v>
+      <c r="E49" s="34" t="s">
+        <v>391</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="29" t="s">
+    <row r="50" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="25" t="s">
         <v>386</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
-      <c r="E50" s="31" t="s">
-        <v>391</v>
+      <c r="E50" s="32" t="s">
+        <v>390</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="29" t="s">
+    <row r="51" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="25" t="s">
         <v>387</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
-      <c r="E51" s="30" t="s">
+      <c r="E51" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="2:8" ht="29.25" x14ac:dyDescent="0.25">
-      <c r="B52" s="29" t="s">
+    <row r="52" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="25" t="s">
         <v>388</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="30" t="s">
+      <c r="E52" s="32" t="s">
         <v>390</v>
       </c>
       <c r="F52" s="7"/>
@@ -2469,12 +2510,12 @@
       <c r="H52" s="7"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="25" t="s">
         <v>389</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
-      <c r="E53" s="30" t="s">
+      <c r="E53" s="26" t="s">
         <v>390</v>
       </c>
       <c r="F53" s="7"/>
@@ -5066,14 +5107,14 @@
       <c r="C5" s="16">
         <v>275</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="27" t="s">
         <v>327</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="28">
         <f>SUM(C5:C35)</f>
         <v>4138</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="28">
         <f>SUM(C5:C21)/72+C35/45</f>
         <v>61.322222222222223</v>
       </c>
@@ -5093,9 +5134,9 @@
       <c r="C6" s="16">
         <v>248</v>
       </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
       <c r="H6" s="7" t="s">
         <v>335</v>
       </c>
@@ -5176,14 +5217,14 @@
       <c r="C10" s="16">
         <v>318</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="27" t="s">
         <v>331</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="29">
         <f>C81</f>
         <v>5160</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="30">
         <f>F10/42</f>
         <v>122.85714285714286</v>
       </c>
@@ -5205,9 +5246,9 @@
       <c r="C11" s="16">
         <v>256</v>
       </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="28"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="7" t="s">
         <v>333</v>
       </c>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95281F31-0DAD-40DB-B0D9-27EAD8D4FED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB78FC8A-AB7B-4FA8-91D2-F3CCB94C73B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="HR" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="395">
   <si>
     <t>직급</t>
   </si>
@@ -1227,6 +1227,9 @@
   </si>
   <si>
     <t>Off (fill form)</t>
+  </si>
+  <si>
+    <t>afternoon</t>
   </si>
 </sst>
 </file>
@@ -1825,7 +1828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D083C086-594E-4C2B-9782-7E24033B84D9}">
-  <dimension ref="B2:H53"/>
+  <dimension ref="A2:H53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -1836,7 +1839,7 @@
     <col min="8" max="8" width="50.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>263</v>
       </c>
@@ -1859,7 +1862,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="25" t="s">
         <v>339</v>
       </c>
@@ -1872,7 +1875,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="25" t="s">
         <v>340</v>
       </c>
@@ -1887,7 +1890,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="25" t="s">
         <v>341</v>
       </c>
@@ -1900,7 +1903,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="5"/>
     </row>
-    <row r="6" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="25" t="s">
         <v>342</v>
       </c>
@@ -1913,7 +1916,7 @@
       <c r="G6" s="6"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="25" t="s">
         <v>343</v>
       </c>
@@ -1926,7 +1929,7 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="25" t="s">
         <v>344</v>
       </c>
@@ -1939,7 +1942,7 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="25" t="s">
         <v>345</v>
       </c>
@@ -1952,7 +1955,7 @@
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="25" t="s">
         <v>346</v>
       </c>
@@ -1965,7 +1968,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="25" t="s">
         <v>347</v>
       </c>
@@ -1978,7 +1981,7 @@
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="25" t="s">
         <v>348</v>
       </c>
@@ -1991,7 +1994,10 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>394</v>
+      </c>
       <c r="B13" s="25" t="s">
         <v>349</v>
       </c>
@@ -2002,7 +2008,7 @@
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="25" t="s">
         <v>350</v>
       </c>
@@ -2015,7 +2021,7 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="25" t="s">
         <v>351</v>
       </c>
@@ -2028,7 +2034,7 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>352</v>
       </c>
@@ -2166,7 +2172,9 @@
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="35"/>
+      <c r="E26" s="32" t="s">
+        <v>390</v>
+      </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
@@ -2249,7 +2257,7 @@
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="25" t="s">
         <v>369</v>
       </c>
@@ -2262,7 +2270,7 @@
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="25" t="s">
         <v>370</v>
       </c>
@@ -2275,7 +2283,7 @@
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="25" t="s">
         <v>371</v>
       </c>
@@ -2288,7 +2296,7 @@
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="25" t="s">
         <v>372</v>
       </c>
@@ -2301,7 +2309,7 @@
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="25" t="s">
         <v>373</v>
       </c>
@@ -2314,7 +2322,7 @@
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="25" t="s">
         <v>374</v>
       </c>
@@ -2327,7 +2335,7 @@
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="25" t="s">
         <v>375</v>
       </c>
@@ -2340,7 +2348,7 @@
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="25" t="s">
         <v>376</v>
       </c>
@@ -2353,7 +2361,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="25" t="s">
         <v>377</v>
       </c>
@@ -2366,7 +2374,7 @@
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="25" t="s">
         <v>378</v>
       </c>
@@ -2379,20 +2387,25 @@
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
     </row>
-    <row r="43" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="25" t="s">
         <v>379</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="35"/>
+      <c r="E43" s="32" t="s">
+        <v>390</v>
+      </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="7" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>394</v>
+      </c>
       <c r="B44" s="25" t="s">
         <v>380</v>
       </c>
@@ -2403,7 +2416,7 @@
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="25" t="s">
         <v>381</v>
       </c>
@@ -2416,7 +2429,7 @@
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="25" t="s">
         <v>382</v>
       </c>
@@ -2431,7 +2444,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="25" t="s">
         <v>383</v>
       </c>
@@ -2444,7 +2457,7 @@
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="25" t="s">
         <v>384</v>
       </c>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB78FC8A-AB7B-4FA8-91D2-F3CCB94C73B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8274736F-52CE-4DD5-AADC-B01D0C818484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="396">
   <si>
     <t>직급</t>
   </si>
@@ -1230,6 +1230,9 @@
   </si>
   <si>
     <t>afternoon</t>
+  </si>
+  <si>
+    <t>Afternoon</t>
   </si>
 </sst>
 </file>
@@ -1464,18 +1467,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1490,6 +1481,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1868,7 +1871,7 @@
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="27" t="s">
         <v>390</v>
       </c>
       <c r="F3" s="6"/>
@@ -1881,7 +1884,7 @@
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F4" s="6"/>
@@ -1896,7 +1899,7 @@
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F5" s="6"/>
@@ -1909,7 +1912,7 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F6" s="6"/>
@@ -1922,7 +1925,7 @@
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F7" s="7"/>
@@ -1935,7 +1938,7 @@
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F8" s="7"/>
@@ -1948,7 +1951,7 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F9" s="7"/>
@@ -1961,7 +1964,7 @@
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="29" t="s">
         <v>393</v>
       </c>
       <c r="F10" s="7"/>
@@ -1974,7 +1977,7 @@
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F11" s="7"/>
@@ -1987,7 +1990,7 @@
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="30" t="s">
         <v>391</v>
       </c>
       <c r="F12" s="7"/>
@@ -2003,7 +2006,9 @@
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="35"/>
+      <c r="E13" s="31" t="s">
+        <v>395</v>
+      </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -2014,7 +2019,7 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F14" s="7"/>
@@ -2027,7 +2032,7 @@
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F15" s="7"/>
@@ -2040,7 +2045,7 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F16" s="7"/>
@@ -2053,7 +2058,7 @@
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F17" s="7"/>
@@ -2066,7 +2071,7 @@
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F18" s="7"/>
@@ -2081,7 +2086,7 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F19" s="7"/>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F20" s="7"/>
@@ -2107,7 +2112,7 @@
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F21" s="7"/>
@@ -2120,7 +2125,7 @@
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F22" s="7"/>
@@ -2133,7 +2138,7 @@
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="32" t="s">
+      <c r="E23" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F23" s="7"/>
@@ -2146,7 +2151,7 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F24" s="7"/>
@@ -2159,7 +2164,7 @@
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F25" s="7"/>
@@ -2172,7 +2177,7 @@
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F26" s="7"/>
@@ -2185,7 +2190,9 @@
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
-      <c r="E27" s="35"/>
+      <c r="E27" s="30" t="s">
+        <v>391</v>
+      </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7" t="s">
@@ -2198,7 +2205,7 @@
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F28" s="7"/>
@@ -2211,7 +2218,7 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
-      <c r="E29" s="32" t="s">
+      <c r="E29" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F29" s="7"/>
@@ -2224,7 +2231,7 @@
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F30" s="7"/>
@@ -2237,7 +2244,7 @@
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
-      <c r="E31" s="34" t="s">
+      <c r="E31" s="30" t="s">
         <v>391</v>
       </c>
       <c r="F31" s="7"/>
@@ -2250,20 +2257,20 @@
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="32" t="s">
+      <c r="E32" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="25" t="s">
         <v>369</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
-      <c r="E33" s="32" t="s">
+      <c r="E33" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F33" s="7"/>
@@ -2276,7 +2283,7 @@
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F34" s="7"/>
@@ -2289,7 +2296,7 @@
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="32" t="s">
+      <c r="E35" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F35" s="7"/>
@@ -2302,7 +2309,7 @@
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="32" t="s">
+      <c r="E36" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F36" s="7"/>
@@ -2315,7 +2322,7 @@
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="32" t="s">
+      <c r="E37" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F37" s="7"/>
@@ -2328,7 +2335,7 @@
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="32" t="s">
+      <c r="E38" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F38" s="7"/>
@@ -2341,7 +2348,7 @@
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="32" t="s">
+      <c r="E39" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F39" s="7"/>
@@ -2354,7 +2361,7 @@
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="32" t="s">
+      <c r="E40" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F40" s="7"/>
@@ -2367,7 +2374,7 @@
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="32" t="s">
+      <c r="E41" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F41" s="7"/>
@@ -2380,7 +2387,7 @@
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="32" t="s">
+      <c r="E42" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F42" s="7"/>
@@ -2393,7 +2400,7 @@
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="32" t="s">
+      <c r="E43" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F43" s="7"/>
@@ -2411,7 +2418,9 @@
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="35"/>
+      <c r="E44" s="31" t="s">
+        <v>395</v>
+      </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
@@ -2422,7 +2431,7 @@
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="32" t="s">
+      <c r="E45" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F45" s="7"/>
@@ -2435,7 +2444,7 @@
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="32" t="s">
+      <c r="E46" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F46" s="7"/>
@@ -2450,7 +2459,7 @@
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="32" t="s">
+      <c r="E47" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F47" s="7"/>
@@ -2463,7 +2472,7 @@
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="32" t="s">
+      <c r="E48" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F48" s="7"/>
@@ -2476,7 +2485,7 @@
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
-      <c r="E49" s="34" t="s">
+      <c r="E49" s="30" t="s">
         <v>391</v>
       </c>
       <c r="F49" s="7"/>
@@ -2489,7 +2498,7 @@
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
-      <c r="E50" s="32" t="s">
+      <c r="E50" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F50" s="7"/>
@@ -2502,7 +2511,7 @@
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
-      <c r="E51" s="32" t="s">
+      <c r="E51" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F51" s="7"/>
@@ -2515,7 +2524,7 @@
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="32" t="s">
+      <c r="E52" s="28" t="s">
         <v>390</v>
       </c>
       <c r="F52" s="7"/>
@@ -5120,14 +5129,14 @@
       <c r="C5" s="16">
         <v>275</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="32" t="s">
         <v>327</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="33">
         <f>SUM(C5:C35)</f>
         <v>4138</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="33">
         <f>SUM(C5:C21)/72+C35/45</f>
         <v>61.322222222222223</v>
       </c>
@@ -5147,9 +5156,9 @@
       <c r="C6" s="16">
         <v>248</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="7" t="s">
         <v>335</v>
       </c>
@@ -5230,14 +5239,14 @@
       <c r="C10" s="16">
         <v>318</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="32" t="s">
         <v>331</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="34">
         <f>C81</f>
         <v>5160</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="35">
         <f>F10/42</f>
         <v>122.85714285714286</v>
       </c>
@@ -5259,9 +5268,9 @@
       <c r="C11" s="16">
         <v>256</v>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="30"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="7" t="s">
         <v>333</v>
       </c>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8274736F-52CE-4DD5-AADC-B01D0C818484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDFBFEC-F1B3-45B3-B953-7F966E02D963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="HR" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="399">
   <si>
     <t>직급</t>
   </si>
@@ -1233,6 +1233,15 @@
   </si>
   <si>
     <t>Afternoon</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Red</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1253,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1306,6 +1315,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF5A3286"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1399,7 +1414,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1493,6 +1508,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2883,458 +2901,539 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{389C6E33-6CBE-4A4F-A438-2E8B726DCE5D}">
-  <dimension ref="B1:F32"/>
+  <dimension ref="B1:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" customWidth="1"/>
-    <col min="4" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E3" s="3">
+      <c r="F3" s="3">
         <v>46217</v>
       </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="3">
+      <c r="F4" s="3">
         <v>46218</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="3">
+      <c r="F5" s="3">
         <v>46223</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E6" s="3">
+      <c r="F6" s="3">
         <v>46225</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="3">
         <v>46226</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>46232</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>46234</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>46237</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="3">
+      <c r="F11" s="3">
         <v>46223</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>46223</v>
       </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E13" s="3">
+      <c r="F13" s="3">
         <v>46238</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>46239</v>
       </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>46241</v>
       </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E16" s="3">
+      <c r="F16" s="3">
         <v>46245</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>46251</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46251</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E19" s="3">
+      <c r="F19" s="3">
         <v>46253</v>
       </c>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>46258</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>46251</v>
       </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>46261</v>
       </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>46252</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>46245</v>
       </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E25" s="3">
+      <c r="F25" s="3">
         <v>46251</v>
       </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>46248</v>
       </c>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E27" s="2"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E28" s="2"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E29" s="2"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E30" s="2"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E31" s="2"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDFBFEC-F1B3-45B3-B953-7F966E02D963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9B86EC-48BE-4EC8-AC31-A52DFE309993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="HR" sheetId="1" r:id="rId1"/>
@@ -1414,7 +1414,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1497,6 +1497,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1509,9 +1512,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -2631,7 +2632,7 @@
         <v>157</v>
       </c>
       <c r="I3" s="6">
-        <v>46249</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
@@ -3091,7 +3092,7 @@
       <c r="B11" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="32" t="s">
         <v>398</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -3109,7 +3110,7 @@
       <c r="B12" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="32" t="s">
         <v>398</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -3147,7 +3148,7 @@
       <c r="B14" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="32" t="s">
         <v>398</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -3193,7 +3194,7 @@
         <v>150</v>
       </c>
       <c r="F16" s="3">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>306</v>
@@ -3281,7 +3282,7 @@
       <c r="B21" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="32" t="s">
         <v>398</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -3299,7 +3300,7 @@
       <c r="B22" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="32" t="s">
         <v>398</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -3355,7 +3356,7 @@
       <c r="B25" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="32" t="s">
         <v>398</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -3373,7 +3374,7 @@
       <c r="B26" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="32" t="s">
         <v>398</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -3442,7 +3443,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A8B69F2-ABF3-479B-9A70-167875A2ADD6}">
-  <dimension ref="B2:H155"/>
+  <dimension ref="B2:H162"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -3491,7 +3492,7 @@
       </c>
       <c r="H4" s="12">
         <f>AVERAGE(D3:D155)</f>
-        <v>4.3290244121951229</v>
+        <v>4.3247619261904777</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
@@ -3509,7 +3510,7 @@
       </c>
       <c r="H5" s="13">
         <f>(H4-H3)/H3</f>
-        <v>-1.6130815410199419E-2</v>
+        <v>-1.7099562229436961E-2</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
@@ -3525,7 +3526,7 @@
       </c>
       <c r="H6" s="11" t="str">
         <f>COUNT(D3:D370)&amp;"FTL"</f>
-        <v>41FTL</v>
+        <v>43FTL</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
@@ -4698,7 +4699,7 @@
       </c>
       <c r="D128" s="8"/>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B129" s="9">
         <v>46202</v>
       </c>
@@ -4710,7 +4711,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B130" s="9">
         <v>46203</v>
       </c>
@@ -4719,7 +4720,7 @@
       </c>
       <c r="D130" s="8"/>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B131" s="9">
         <v>46204</v>
       </c>
@@ -4728,7 +4729,7 @@
       </c>
       <c r="D131" s="8"/>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B132" s="9">
         <v>46205</v>
       </c>
@@ -4739,7 +4740,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B133" s="9">
         <v>46209</v>
       </c>
@@ -4748,7 +4749,7 @@
       </c>
       <c r="D133" s="8"/>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B134" s="9">
         <v>46210</v>
       </c>
@@ -4757,7 +4758,7 @@
       </c>
       <c r="D134" s="8"/>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B135" s="9">
         <v>46211</v>
       </c>
@@ -4766,7 +4767,7 @@
       </c>
       <c r="D135" s="8"/>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B136" s="9">
         <v>46212</v>
       </c>
@@ -4775,7 +4776,7 @@
       </c>
       <c r="D136" s="8"/>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B137" s="9">
         <v>46213</v>
       </c>
@@ -4786,7 +4787,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B138" s="9">
         <v>46216</v>
       </c>
@@ -4798,7 +4799,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B139" s="9">
         <v>46217</v>
       </c>
@@ -4807,7 +4808,7 @@
       </c>
       <c r="D139" s="8"/>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B140" s="9">
         <v>46218</v>
       </c>
@@ -4816,7 +4817,7 @@
       </c>
       <c r="D140" s="8"/>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B141" s="9">
         <v>46219</v>
       </c>
@@ -4825,7 +4826,7 @@
       </c>
       <c r="D141" s="8"/>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B142" s="9">
         <v>46220</v>
       </c>
@@ -4836,8 +4837,9 @@
       <c r="E142">
         <v>3.97</v>
       </c>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G142" s="37"/>
+    </row>
+    <row r="143" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B143" s="9">
         <v>46223</v>
       </c>
@@ -4850,8 +4852,9 @@
       <c r="E143">
         <v>4.17</v>
       </c>
-    </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G143" s="37"/>
+    </row>
+    <row r="144" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B144" s="9">
         <v>46224</v>
       </c>
@@ -4862,8 +4865,9 @@
       <c r="E144">
         <v>4.1500000000000004</v>
       </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G144" s="37"/>
+    </row>
+    <row r="145" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B145" s="9">
         <v>46225</v>
       </c>
@@ -4874,8 +4878,9 @@
       <c r="E145">
         <v>4.16</v>
       </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G145" s="37"/>
+    </row>
+    <row r="146" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B146" s="9">
         <v>46226</v>
       </c>
@@ -4889,8 +4894,9 @@
       <c r="F146">
         <v>4.26</v>
       </c>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G146" s="37"/>
+    </row>
+    <row r="147" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B147" s="9">
         <v>46227</v>
       </c>
@@ -4901,8 +4907,9 @@
       <c r="E147">
         <v>4.04</v>
       </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G147" s="37"/>
+    </row>
+    <row r="148" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B148" s="9">
         <v>46230</v>
       </c>
@@ -4915,8 +4922,9 @@
       <c r="E148">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G148" s="37"/>
+    </row>
+    <row r="149" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B149" s="9">
         <v>46231</v>
       </c>
@@ -4927,8 +4935,9 @@
       <c r="E149">
         <v>3.96</v>
       </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G149" s="37"/>
+    </row>
+    <row r="150" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B150" s="9">
         <v>46232</v>
       </c>
@@ -4939,8 +4948,9 @@
       <c r="E150">
         <v>3.99</v>
       </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G150" s="37"/>
+    </row>
+    <row r="151" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B151" s="9">
         <v>46233</v>
       </c>
@@ -4954,20 +4964,24 @@
       <c r="F151">
         <v>4.28</v>
       </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G151" s="37"/>
+    </row>
+    <row r="152" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B152" s="9">
         <v>46234</v>
       </c>
       <c r="C152" s="8">
         <v>4.2299999999999995</v>
       </c>
-      <c r="D152" s="8"/>
+      <c r="D152" s="8">
+        <v>4.1500000000000004</v>
+      </c>
       <c r="E152">
         <v>4.05</v>
       </c>
-    </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G152" s="37"/>
+    </row>
+    <row r="153" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B153" s="9">
         <v>46237</v>
       </c>
@@ -4978,8 +4992,9 @@
       <c r="E153">
         <v>4.04</v>
       </c>
-    </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G153" s="37"/>
+    </row>
+    <row r="154" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B154" s="9">
         <v>46238</v>
       </c>
@@ -4990,8 +5005,9 @@
       <c r="E154">
         <v>4.05</v>
       </c>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G154" s="37"/>
+    </row>
+    <row r="155" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B155" s="9">
         <v>46239</v>
       </c>
@@ -5001,6 +5017,69 @@
       <c r="D155" s="8"/>
       <c r="E155">
         <v>3.98</v>
+      </c>
+      <c r="G155" s="37"/>
+    </row>
+    <row r="156" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B156" s="9">
+        <v>46240</v>
+      </c>
+      <c r="C156" s="8">
+        <f>E156+0.18</f>
+        <v>4.1999999999999993</v>
+      </c>
+      <c r="D156" s="8"/>
+      <c r="E156">
+        <v>4.0199999999999996</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B157" s="9">
+        <v>46241</v>
+      </c>
+      <c r="C157" s="8">
+        <f t="shared" ref="C157:C159" si="0">E157+0.18</f>
+        <v>4.12</v>
+      </c>
+      <c r="D157" s="8"/>
+      <c r="E157">
+        <v>3.94</v>
+      </c>
+      <c r="F157">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="158" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B158" s="9">
+        <v>46244</v>
+      </c>
+      <c r="C158" s="8">
+        <f t="shared" si="0"/>
+        <v>4.18</v>
+      </c>
+      <c r="D158" s="8">
+        <v>4.16</v>
+      </c>
+      <c r="E158">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B159" s="9">
+        <v>46245</v>
+      </c>
+      <c r="C159" s="8">
+        <f t="shared" si="0"/>
+        <v>4.3199999999999994</v>
+      </c>
+      <c r="D159" s="8"/>
+      <c r="E159">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
+    <row r="162" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F162">
+        <v>4.16</v>
       </c>
     </row>
   </sheetData>
@@ -5228,14 +5307,14 @@
       <c r="C5" s="16">
         <v>275</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="34">
         <f>SUM(C5:C35)</f>
         <v>4138</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="34">
         <f>SUM(C5:C21)/72+C35/45</f>
         <v>61.322222222222223</v>
       </c>
@@ -5255,9 +5334,9 @@
       <c r="C6" s="16">
         <v>248</v>
       </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="7" t="s">
         <v>335</v>
       </c>
@@ -5338,14 +5417,14 @@
       <c r="C10" s="16">
         <v>318</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="33" t="s">
         <v>331</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="35">
         <f>C81</f>
         <v>5160</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="36">
         <f>F10/42</f>
         <v>122.85714285714286</v>
       </c>
@@ -5367,9 +5446,9 @@
       <c r="C11" s="16">
         <v>256</v>
       </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="36"/>
       <c r="H11" s="7" t="s">
         <v>333</v>
       </c>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9B86EC-48BE-4EC8-AC31-A52DFE309993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED99F1A4-7A3F-44A2-A989-10AA850D8011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="HR" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="398">
   <si>
     <t>직급</t>
   </si>
@@ -1100,9 +1100,6 @@
     <t>Erika Contreras</t>
   </si>
   <si>
-    <t>Esmeralda Hernandez Santos</t>
-  </si>
-  <si>
     <t>Evelia Garcia Martinez</t>
   </si>
   <si>
@@ -1232,9 +1229,6 @@
     <t>afternoon</t>
   </si>
   <si>
-    <t>Afternoon</t>
-  </si>
-  <si>
     <t>Color</t>
   </si>
   <si>
@@ -1242,6 +1236,9 @@
   </si>
   <si>
     <t>Red</t>
+  </si>
+  <si>
+    <t>Late; call in</t>
   </si>
 </sst>
 </file>
@@ -1253,7 +1250,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1321,6 +1318,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3D3D3D"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1414,7 +1417,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1500,6 +1503,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1512,7 +1516,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -1885,132 +1897,132 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="38" t="s">
         <v>339</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
       <c r="E3" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="39" t="s">
         <v>340</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="39" t="s">
         <v>341</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="39" t="s">
         <v>342</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="39" t="s">
         <v>343</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="39" t="s">
         <v>344</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="39" t="s">
         <v>345</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="39" t="s">
         <v>346</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="29" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="25" t="s">
+    <row r="11" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="39" t="s">
         <v>347</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="39" t="s">
         <v>348</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="30" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -2018,185 +2030,186 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>394</v>
-      </c>
-      <c r="B13" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="B13" s="39" t="s">
         <v>349</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="31" t="s">
-        <v>395</v>
+      <c r="E13" s="31" t="str">
+        <f>A13</f>
+        <v>afternoon</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="39" t="s">
         <v>350</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="25" t="s">
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="39" t="s">
         <v>351</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="39" t="s">
         <v>352</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="25" t="s">
+    <row r="17" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="39" t="s">
         <v>353</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="25" t="s">
+    <row r="18" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="39" t="s">
         <v>354</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="25" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="39" t="s">
         <v>355</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="25" t="s">
+    <row r="20" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="39" t="s">
         <v>356</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="39" t="s">
         <v>357</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="39" t="s">
         <v>358</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="39" t="s">
         <v>359</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="25" t="s">
+    <row r="24" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="39" t="s">
         <v>360</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="25" t="s">
+    <row r="25" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="39" t="s">
         <v>361</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
     <row r="26" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="39" t="s">
         <v>362</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="28" t="s">
+      <c r="E26" s="30" t="s">
         <v>390</v>
       </c>
       <c r="F26" s="7"/>
@@ -2204,267 +2217,272 @@
       <c r="H26" s="7"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="39" t="s">
         <v>363</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="30" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="39" t="s">
         <v>364</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
     </row>
     <row r="29" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="39" t="s">
         <v>365</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
     </row>
     <row r="30" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="39" t="s">
         <v>366</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
     <row r="31" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="39" t="s">
         <v>367</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="30" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="25" t="s">
+    <row r="32" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="39" t="s">
         <v>368</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="25" t="s">
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="39" t="s">
         <v>369</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="39" t="s">
         <v>370</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="25" t="s">
+    <row r="35" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="39" t="s">
         <v>371</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="25" t="s">
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="39" t="s">
         <v>372</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="39" t="s">
         <v>373</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="39" t="s">
         <v>374</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="39" t="s">
         <v>375</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="25" t="s">
+    <row r="40" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="39" t="s">
         <v>376</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="25" t="s">
+    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="39" t="s">
         <v>377</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="25" t="s">
+      <c r="B42" s="39" t="s">
         <v>378</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="25" t="s">
+      <c r="A43" t="s">
+        <v>393</v>
+      </c>
+      <c r="B43" s="39" t="s">
         <v>379</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="28" t="s">
-        <v>390</v>
+      <c r="E43" s="31" t="str">
+        <f>A43</f>
+        <v>afternoon</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>394</v>
-      </c>
-      <c r="B44" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="B44" s="39" t="s">
         <v>380</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="31" t="s">
-        <v>395</v>
+      <c r="E44" s="31" t="str">
+        <f>A44</f>
+        <v>afternoon</v>
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="25" t="s">
+    <row r="45" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="39" t="s">
         <v>381</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="28" t="s">
-        <v>390</v>
+      <c r="E45" s="40" t="s">
+        <v>397</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="39" t="s">
         <v>382</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -2472,79 +2490,79 @@
         <v>267</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="25" t="s">
+    <row r="47" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="39" t="s">
         <v>383</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="25" t="s">
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="39" t="s">
         <v>384</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
     </row>
     <row r="49" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="39" t="s">
         <v>385</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="30" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
     </row>
-    <row r="50" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="25" t="s">
+    <row r="50" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="39" t="s">
         <v>386</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
-      <c r="E50" s="28" t="s">
-        <v>390</v>
+      <c r="E50" s="29" t="s">
+        <v>392</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="25" t="s">
+    <row r="51" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="39" t="s">
         <v>387</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="25" t="s">
+    <row r="52" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="39" t="s">
         <v>388</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -2552,12 +2570,12 @@
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B53" s="25" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="26" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
@@ -2917,7 +2935,7 @@
         <v>299</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>300</v>
@@ -2937,7 +2955,7 @@
         <v>299</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>301</v>
@@ -2955,7 +2973,7 @@
         <v>299</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>149</v>
@@ -2975,7 +2993,7 @@
         <v>299</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>149</v>
@@ -2995,7 +3013,7 @@
         <v>299</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>149</v>
@@ -3015,7 +3033,7 @@
         <v>299</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>149</v>
@@ -3035,7 +3053,7 @@
         <v>299</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>301</v>
@@ -3053,7 +3071,7 @@
         <v>299</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>149</v>
@@ -3073,7 +3091,7 @@
         <v>299</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>149</v>
@@ -3093,7 +3111,7 @@
         <v>299</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>152</v>
@@ -3111,7 +3129,7 @@
         <v>299</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>151</v>
@@ -3129,7 +3147,7 @@
         <v>299</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>149</v>
@@ -3149,7 +3167,7 @@
         <v>299</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>153</v>
@@ -3167,7 +3185,7 @@
         <v>299</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>301</v>
@@ -3185,7 +3203,7 @@
         <v>299</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>149</v>
@@ -3205,7 +3223,7 @@
         <v>299</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>149</v>
@@ -3225,7 +3243,7 @@
         <v>299</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>149</v>
@@ -3245,7 +3263,7 @@
         <v>299</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>301</v>
@@ -3263,7 +3281,7 @@
         <v>299</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>149</v>
@@ -3283,7 +3301,7 @@
         <v>299</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>154</v>
@@ -3301,7 +3319,7 @@
         <v>299</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>155</v>
@@ -3319,7 +3337,7 @@
         <v>299</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>149</v>
@@ -3339,7 +3357,7 @@
         <v>299</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>162</v>
@@ -3357,7 +3375,7 @@
         <v>299</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>152</v>
@@ -3375,7 +3393,7 @@
         <v>299</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>338</v>
@@ -3476,7 +3494,8 @@
         <v>318</v>
       </c>
       <c r="H3" s="12">
-        <v>4.4000000000000004</v>
+        <f>AVERAGE(C3:C602)</f>
+        <v>4.3956050955414003</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
@@ -3491,8 +3510,8 @@
         <v>319</v>
       </c>
       <c r="H4" s="12">
-        <f>AVERAGE(D3:D155)</f>
-        <v>4.3247619261904777</v>
+        <f>AVERAGE(D3:D745)</f>
+        <v>4.3209302534883731</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
@@ -3510,7 +3529,7 @@
       </c>
       <c r="H5" s="13">
         <f>(H4-H3)/H3</f>
-        <v>-1.7099562229436961E-2</v>
+        <v>-1.6988523861884736E-2</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
@@ -4837,7 +4856,7 @@
       <c r="E142">
         <v>3.97</v>
       </c>
-      <c r="G142" s="37"/>
+      <c r="G142" s="33"/>
     </row>
     <row r="143" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B143" s="9">
@@ -4852,7 +4871,7 @@
       <c r="E143">
         <v>4.17</v>
       </c>
-      <c r="G143" s="37"/>
+      <c r="G143" s="33"/>
     </row>
     <row r="144" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B144" s="9">
@@ -4865,7 +4884,7 @@
       <c r="E144">
         <v>4.1500000000000004</v>
       </c>
-      <c r="G144" s="37"/>
+      <c r="G144" s="33"/>
     </row>
     <row r="145" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B145" s="9">
@@ -4878,7 +4897,7 @@
       <c r="E145">
         <v>4.16</v>
       </c>
-      <c r="G145" s="37"/>
+      <c r="G145" s="33"/>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B146" s="9">
@@ -4894,7 +4913,7 @@
       <c r="F146">
         <v>4.26</v>
       </c>
-      <c r="G146" s="37"/>
+      <c r="G146" s="33"/>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B147" s="9">
@@ -4907,7 +4926,7 @@
       <c r="E147">
         <v>4.04</v>
       </c>
-      <c r="G147" s="37"/>
+      <c r="G147" s="33"/>
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B148" s="9">
@@ -4922,7 +4941,7 @@
       <c r="E148">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G148" s="37"/>
+      <c r="G148" s="33"/>
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B149" s="9">
@@ -4935,7 +4954,7 @@
       <c r="E149">
         <v>3.96</v>
       </c>
-      <c r="G149" s="37"/>
+      <c r="G149" s="33"/>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B150" s="9">
@@ -4948,7 +4967,7 @@
       <c r="E150">
         <v>3.99</v>
       </c>
-      <c r="G150" s="37"/>
+      <c r="G150" s="33"/>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B151" s="9">
@@ -4964,7 +4983,7 @@
       <c r="F151">
         <v>4.28</v>
       </c>
-      <c r="G151" s="37"/>
+      <c r="G151" s="33"/>
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B152" s="9">
@@ -4979,7 +4998,7 @@
       <c r="E152">
         <v>4.05</v>
       </c>
-      <c r="G152" s="37"/>
+      <c r="G152" s="33"/>
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B153" s="9">
@@ -4992,7 +5011,7 @@
       <c r="E153">
         <v>4.04</v>
       </c>
-      <c r="G153" s="37"/>
+      <c r="G153" s="33"/>
     </row>
     <row r="154" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B154" s="9">
@@ -5005,7 +5024,7 @@
       <c r="E154">
         <v>4.05</v>
       </c>
-      <c r="G154" s="37"/>
+      <c r="G154" s="33"/>
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B155" s="9">
@@ -5018,7 +5037,7 @@
       <c r="E155">
         <v>3.98</v>
       </c>
-      <c r="G155" s="37"/>
+      <c r="G155" s="33"/>
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B156" s="9">
@@ -5307,14 +5326,14 @@
       <c r="C5" s="16">
         <v>275</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <f>SUM(C5:C35)</f>
         <v>4138</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="35">
         <f>SUM(C5:C21)/72+C35/45</f>
         <v>61.322222222222223</v>
       </c>
@@ -5334,9 +5353,9 @@
       <c r="C6" s="16">
         <v>248</v>
       </c>
-      <c r="E6" s="33"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
       <c r="H6" s="7" t="s">
         <v>335</v>
       </c>
@@ -5417,14 +5436,14 @@
       <c r="C10" s="16">
         <v>318</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="34" t="s">
         <v>331</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="36">
         <f>C81</f>
         <v>5160</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="37">
         <f>F10/42</f>
         <v>122.85714285714286</v>
       </c>
@@ -5446,9 +5465,9 @@
       <c r="C11" s="16">
         <v>256</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="36"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="7" t="s">
         <v>333</v>
       </c>

--- a/dashboard raw data.xlsx
+++ b/dashboard raw data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\insan\Desktop\대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED99F1A4-7A3F-44A2-A989-10AA850D8011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A2E456-AE40-46EB-B4DA-C1DD6CDB179E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9A895445-513A-45F2-B3AD-994EE0A25D8E}"/>
   </bookViews>
   <sheets>
     <sheet name="HR" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="397">
   <si>
     <t>직급</t>
   </si>
@@ -938,9 +938,6 @@
     <t>End of Aug, End of Sep</t>
   </si>
   <si>
-    <t>Begining of Aug</t>
-  </si>
-  <si>
     <t>Order Date</t>
   </si>
   <si>
@@ -1220,12 +1217,6 @@
     <t>Vacation</t>
   </si>
   <si>
-    <t>Pregnant</t>
-  </si>
-  <si>
-    <t>Off (fill form)</t>
-  </si>
-  <si>
     <t>afternoon</t>
   </si>
   <si>
@@ -1238,7 +1229,13 @@
     <t>Red</t>
   </si>
   <si>
-    <t>Late; call in</t>
+    <t>Day Off</t>
+  </si>
+  <si>
+    <t>Late; no call</t>
+  </si>
+  <si>
+    <t>2nd week of Sep</t>
   </si>
 </sst>
 </file>
@@ -1250,7 +1247,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1306,12 +1303,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF5A3286"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1417,7 +1408,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1479,19 +1470,7 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1500,10 +1479,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1516,13 +1504,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1862,7 +1844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D083C086-594E-4C2B-9782-7E24033B84D9}">
-  <dimension ref="A2:H53"/>
+  <dimension ref="A2:H52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -1897,132 +1879,130 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>339</v>
+      <c r="B3" s="30" t="s">
+        <v>338</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="27" t="s">
-        <v>389</v>
+      <c r="E3" s="37" t="s">
+        <v>394</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="39" t="s">
-        <v>340</v>
+      <c r="B4" s="31" t="s">
+        <v>339</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="28" t="s">
-        <v>389</v>
+      <c r="E4" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="7" t="s">
-        <v>391</v>
-      </c>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="39" t="s">
-        <v>341</v>
+      <c r="B5" s="31" t="s">
+        <v>340</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="28" t="s">
-        <v>389</v>
+      <c r="E5" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="39" t="s">
-        <v>342</v>
+      <c r="B6" s="31" t="s">
+        <v>341</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="28" t="s">
-        <v>389</v>
+      <c r="E6" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="39" t="s">
-        <v>343</v>
+      <c r="B7" s="31" t="s">
+        <v>342</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="28" t="s">
-        <v>389</v>
+      <c r="E7" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="39" t="s">
-        <v>344</v>
+      <c r="B8" s="31" t="s">
+        <v>343</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="28" t="s">
-        <v>389</v>
+      <c r="E8" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="39" t="s">
-        <v>345</v>
+      <c r="B9" s="31" t="s">
+        <v>344</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="28" t="s">
-        <v>389</v>
+      <c r="E9" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="39" t="s">
-        <v>346</v>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="31" t="s">
+        <v>345</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="29" t="s">
-        <v>392</v>
+      <c r="E10" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="39" t="s">
-        <v>347</v>
+      <c r="B11" s="31" t="s">
+        <v>346</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="28" t="s">
-        <v>389</v>
+      <c r="E11" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="39" t="s">
-        <v>348</v>
+      <c r="B12" s="31" t="s">
+        <v>347</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="30" t="s">
-        <v>390</v>
+      <c r="E12" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -2030,397 +2010,392 @@
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>393</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>349</v>
+        <v>390</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>348</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="31" t="str">
-        <f>A13</f>
-        <v>afternoon</v>
+      <c r="E13" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="39" t="s">
-        <v>350</v>
+      <c r="B14" s="31" t="s">
+        <v>349</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="28" t="s">
-        <v>389</v>
+      <c r="E14" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="39" t="s">
-        <v>351</v>
+      <c r="B15" s="31" t="s">
+        <v>350</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="28" t="s">
-        <v>389</v>
+      <c r="E15" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="39" t="s">
-        <v>352</v>
+      <c r="B16" s="31" t="s">
+        <v>351</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="28" t="s">
-        <v>389</v>
+      <c r="E16" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="39" t="s">
-        <v>353</v>
+      <c r="B17" s="31" t="s">
+        <v>352</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="28" t="s">
-        <v>389</v>
+      <c r="E17" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
     </row>
     <row r="18" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="39" t="s">
-        <v>354</v>
+      <c r="B18" s="31" t="s">
+        <v>353</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
-      <c r="E18" s="28" t="s">
-        <v>389</v>
+      <c r="E18" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="7" t="s">
-        <v>391</v>
-      </c>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="39" t="s">
-        <v>355</v>
+      <c r="B19" s="31" t="s">
+        <v>354</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="28" t="s">
-        <v>389</v>
+      <c r="E19" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="39" t="s">
-        <v>356</v>
+      <c r="B20" s="31" t="s">
+        <v>355</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="28" t="s">
-        <v>389</v>
+      <c r="E20" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="39" t="s">
-        <v>357</v>
+      <c r="B21" s="31" t="s">
+        <v>356</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="28" t="s">
-        <v>389</v>
+      <c r="E21" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="39" t="s">
-        <v>358</v>
+      <c r="B22" s="31" t="s">
+        <v>357</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
-      <c r="E22" s="28" t="s">
-        <v>389</v>
+      <c r="E22" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="39" t="s">
-        <v>359</v>
+      <c r="B23" s="31" t="s">
+        <v>358</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="28" t="s">
-        <v>389</v>
+      <c r="E23" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="39" t="s">
-        <v>360</v>
+      <c r="B24" s="31" t="s">
+        <v>359</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="28" t="s">
-        <v>389</v>
+      <c r="E24" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
     <row r="25" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="39" t="s">
-        <v>361</v>
+      <c r="B25" s="31" t="s">
+        <v>360</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="28" t="s">
-        <v>389</v>
+      <c r="E25" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
     <row r="26" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="39" t="s">
-        <v>362</v>
+      <c r="B26" s="31" t="s">
+        <v>361</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="30" t="s">
-        <v>390</v>
+      <c r="E26" s="26" t="s">
+        <v>389</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="39" t="s">
-        <v>363</v>
+      <c r="B27" s="31" t="s">
+        <v>362</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
-      <c r="E27" s="30" t="s">
-        <v>390</v>
+      <c r="E27" s="26" t="s">
+        <v>389</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
-      <c r="H27" s="7" t="s">
-        <v>391</v>
-      </c>
+      <c r="H27" s="7"/>
     </row>
     <row r="28" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="39" t="s">
-        <v>364</v>
+      <c r="B28" s="31" t="s">
+        <v>363</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="28" t="s">
-        <v>389</v>
+      <c r="E28" s="37" t="s">
+        <v>394</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="39" t="s">
-        <v>365</v>
+    <row r="29" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="31" t="s">
+        <v>364</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
-      <c r="E29" s="28" t="s">
-        <v>389</v>
+      <c r="E29" s="25" t="s">
+        <v>395</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
     </row>
     <row r="30" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="39" t="s">
-        <v>366</v>
+      <c r="B30" s="31" t="s">
+        <v>365</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
-      <c r="E30" s="28" t="s">
-        <v>389</v>
+      <c r="E30" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
     <row r="31" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="39" t="s">
-        <v>367</v>
+      <c r="B31" s="31" t="s">
+        <v>366</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
-      <c r="E31" s="30" t="s">
-        <v>390</v>
+      <c r="E31" s="26" t="s">
+        <v>389</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
     </row>
     <row r="32" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="39" t="s">
-        <v>368</v>
+      <c r="B32" s="31" t="s">
+        <v>367</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
-      <c r="E32" s="28" t="s">
-        <v>389</v>
+      <c r="E32" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="39" t="s">
-        <v>369</v>
+      <c r="B33" s="31" t="s">
+        <v>368</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
-      <c r="E33" s="28" t="s">
-        <v>389</v>
+      <c r="E33" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="39" t="s">
-        <v>370</v>
+      <c r="B34" s="31" t="s">
+        <v>369</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
-      <c r="E34" s="28" t="s">
-        <v>389</v>
+      <c r="E34" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
     </row>
     <row r="35" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="39" t="s">
-        <v>371</v>
+      <c r="B35" s="31" t="s">
+        <v>370</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
-      <c r="E35" s="28" t="s">
-        <v>389</v>
+      <c r="E35" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="39" t="s">
-        <v>372</v>
+      <c r="B36" s="31" t="s">
+        <v>371</v>
       </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c r="E36" s="28" t="s">
-        <v>389</v>
+      <c r="E36" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="39" t="s">
-        <v>373</v>
+      <c r="B37" s="31" t="s">
+        <v>372</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
-      <c r="E37" s="28" t="s">
-        <v>389</v>
+      <c r="E37" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="39" t="s">
-        <v>374</v>
+      <c r="B38" s="31" t="s">
+        <v>373</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="28" t="s">
-        <v>389</v>
+      <c r="E38" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="39" t="s">
-        <v>375</v>
+      <c r="B39" s="31" t="s">
+        <v>374</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
-      <c r="E39" s="28" t="s">
-        <v>389</v>
+      <c r="E39" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
     </row>
     <row r="40" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="39" t="s">
-        <v>376</v>
+      <c r="B40" s="31" t="s">
+        <v>375</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
-      <c r="E40" s="28" t="s">
-        <v>389</v>
+      <c r="E40" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="39" t="s">
-        <v>377</v>
+      <c r="B41" s="31" t="s">
+        <v>376</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="28" t="s">
-        <v>389</v>
+      <c r="E41" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="39" t="s">
-        <v>378</v>
+      <c r="B42" s="31" t="s">
+        <v>377</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
-      <c r="E42" s="28" t="s">
-        <v>389</v>
+      <c r="E42" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -2428,33 +2403,30 @@
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>393</v>
-      </c>
-      <c r="B43" s="39" t="s">
-        <v>379</v>
+        <v>390</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>378</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
-      <c r="E43" s="31" t="str">
-        <f>A43</f>
-        <v>afternoon</v>
+      <c r="E43" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
-      <c r="H43" s="7" t="s">
-        <v>391</v>
-      </c>
+      <c r="H43" s="7"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>393</v>
-      </c>
-      <c r="B44" s="39" t="s">
-        <v>380</v>
+        <v>390</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>379</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="31" t="str">
+      <c r="E44" s="27" t="str">
         <f>A44</f>
         <v>afternoon</v>
       </c>
@@ -2462,124 +2434,111 @@
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="39" t="s">
-        <v>381</v>
+    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="31" t="s">
+        <v>380</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c r="E45" s="40" t="s">
-        <v>397</v>
+      <c r="E45" s="37" t="s">
+        <v>394</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
+      <c r="H45" s="7" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="39" t="s">
-        <v>382</v>
+      <c r="B46" s="31" t="s">
+        <v>381</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
-      <c r="E46" s="28" t="s">
-        <v>389</v>
+      <c r="E46" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
-      <c r="H46" s="5" t="s">
-        <v>267</v>
-      </c>
+      <c r="H46" s="5"/>
     </row>
     <row r="47" spans="1:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="39" t="s">
-        <v>383</v>
+      <c r="B47" s="31" t="s">
+        <v>382</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="28" t="s">
-        <v>389</v>
+      <c r="E47" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="39" t="s">
-        <v>384</v>
+      <c r="B48" s="31" t="s">
+        <v>383</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="28" t="s">
-        <v>389</v>
+      <c r="E48" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
     </row>
     <row r="49" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="39" t="s">
-        <v>385</v>
+      <c r="B49" s="31" t="s">
+        <v>384</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
-      <c r="E49" s="30" t="s">
-        <v>390</v>
+      <c r="E49" s="26" t="s">
+        <v>389</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
     </row>
-    <row r="50" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="39" t="s">
-        <v>386</v>
+    <row r="50" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="31" t="s">
+        <v>385</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
-      <c r="E50" s="29" t="s">
-        <v>392</v>
+      <c r="E50" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
     <row r="51" spans="2:8" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="39" t="s">
-        <v>387</v>
+      <c r="B51" s="31" t="s">
+        <v>386</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
-      <c r="E51" s="28" t="s">
-        <v>389</v>
+      <c r="E51" s="25" t="s">
+        <v>388</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
     </row>
     <row r="52" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="39" t="s">
-        <v>388</v>
+      <c r="B52" s="31" t="s">
+        <v>387</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="28" t="s">
-        <v>389</v>
+      <c r="E52" s="32" t="s">
+        <v>394</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="25" t="s">
-        <v>388</v>
-      </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="26" t="s">
-        <v>389</v>
-      </c>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2624,7 +2583,7 @@
         <v>293</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
@@ -2780,7 +2739,7 @@
         <v>295</v>
       </c>
       <c r="I8" s="6">
-        <v>46251</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
@@ -2881,10 +2840,10 @@
         <v>292</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>297</v>
+        <v>396</v>
       </c>
       <c r="I12" s="6">
-        <v>46249</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="28.5" x14ac:dyDescent="0.25">
@@ -2932,19 +2891,19 @@
     <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E2" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>266</v>
@@ -2952,13 +2911,13 @@
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>150</v>
@@ -2970,10 +2929,10 @@
     </row>
     <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>149</v>
@@ -2985,15 +2944,15 @@
         <v>46218</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>149</v>
@@ -3005,15 +2964,15 @@
         <v>46223</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>149</v>
@@ -3025,15 +2984,15 @@
         <v>46225</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>149</v>
@@ -3045,18 +3004,18 @@
         <v>46226</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>150</v>
@@ -3068,10 +3027,10 @@
     </row>
     <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>149</v>
@@ -3083,15 +3042,15 @@
         <v>46234</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>149</v>
@@ -3103,15 +3062,15 @@
         <v>46237</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>396</v>
+        <v>298</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>393</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>152</v>
@@ -3126,10 +3085,10 @@
     </row>
     <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>396</v>
+        <v>298</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>393</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>151</v>
@@ -3144,10 +3103,10 @@
     </row>
     <row r="13" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>149</v>
@@ -3159,15 +3118,15 @@
         <v>46238</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>396</v>
+        <v>298</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>393</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>153</v>
@@ -3182,13 +3141,13 @@
     </row>
     <row r="15" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>150</v>
@@ -3200,10 +3159,10 @@
     </row>
     <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>149</v>
@@ -3215,15 +3174,15 @@
         <v>46246</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>149</v>
@@ -3235,15 +3194,15 @@
         <v>46251</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>149</v>
@@ -3255,18 +3214,18 @@
         <v>46251</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>150</v>
@@ -3278,10 +3237,10 @@
     </row>
     <row r="20" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>149</v>
@@ -3293,15 +3252,15 @@
         <v>46258</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>396</v>
+        <v>298</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>393</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>154</v>
@@ -3316,10 +3275,10 @@
     </row>
     <row r="22" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>396</v>
+        <v>298</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>393</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>155</v>
@@ -3334,10 +3293,10 @@
     </row>
     <row r="23" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>149</v>
@@ -3349,15 +3308,15 @@
         <v>46252</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>162</v>
@@ -3372,10 +3331,10 @@
     </row>
     <row r="25" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>396</v>
+        <v>298</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>393</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>152</v>
@@ -3390,13 +3349,13 @@
     </row>
     <row r="26" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>396</v>
+        <v>298</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>393</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>150</v>
@@ -3473,13 +3432,13 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>316</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
@@ -3491,7 +3450,7 @@
       </c>
       <c r="D3" s="8"/>
       <c r="G3" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H3" s="12">
         <f>AVERAGE(C3:C602)</f>
@@ -3507,7 +3466,7 @@
       </c>
       <c r="D4" s="8"/>
       <c r="G4" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H4" s="12">
         <f>AVERAGE(D3:D745)</f>
@@ -3525,7 +3484,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H5" s="13">
         <f>(H4-H3)/H3</f>
@@ -3541,7 +3500,7 @@
       </c>
       <c r="D6" s="8"/>
       <c r="G6" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H6" s="11" t="str">
         <f>COUNT(D3:D370)&amp;"FTL"</f>
@@ -4856,7 +4815,7 @@
       <c r="E142">
         <v>3.97</v>
       </c>
-      <c r="G142" s="33"/>
+      <c r="G142" s="29"/>
     </row>
     <row r="143" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B143" s="9">
@@ -4871,7 +4830,7 @@
       <c r="E143">
         <v>4.17</v>
       </c>
-      <c r="G143" s="33"/>
+      <c r="G143" s="29"/>
     </row>
     <row r="144" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B144" s="9">
@@ -4884,7 +4843,7 @@
       <c r="E144">
         <v>4.1500000000000004</v>
       </c>
-      <c r="G144" s="33"/>
+      <c r="G144" s="29"/>
     </row>
     <row r="145" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B145" s="9">
@@ -4897,7 +4856,7 @@
       <c r="E145">
         <v>4.16</v>
       </c>
-      <c r="G145" s="33"/>
+      <c r="G145" s="29"/>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B146" s="9">
@@ -4913,7 +4872,7 @@
       <c r="F146">
         <v>4.26</v>
       </c>
-      <c r="G146" s="33"/>
+      <c r="G146" s="29"/>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B147" s="9">
@@ -4926,7 +4885,7 @@
       <c r="E147">
         <v>4.04</v>
       </c>
-      <c r="G147" s="33"/>
+      <c r="G147" s="29"/>
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B148" s="9">
@@ -4941,7 +4900,7 @@
       <c r="E148">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G148" s="33"/>
+      <c r="G148" s="29"/>
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B149" s="9">
@@ -4954,7 +4913,7 @@
       <c r="E149">
         <v>3.96</v>
       </c>
-      <c r="G149" s="33"/>
+      <c r="G149" s="29"/>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B150" s="9">
@@ -4967,7 +4926,7 @@
       <c r="E150">
         <v>3.99</v>
       </c>
-      <c r="G150" s="33"/>
+      <c r="G150" s="29"/>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B151" s="9">
@@ -4983,7 +4942,7 @@
       <c r="F151">
         <v>4.28</v>
       </c>
-      <c r="G151" s="33"/>
+      <c r="G151" s="29"/>
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B152" s="9">
@@ -4998,7 +4957,7 @@
       <c r="E152">
         <v>4.05</v>
       </c>
-      <c r="G152" s="33"/>
+      <c r="G152" s="29"/>
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B153" s="9">
@@ -5011,7 +4970,7 @@
       <c r="E153">
         <v>4.04</v>
       </c>
-      <c r="G153" s="33"/>
+      <c r="G153" s="29"/>
     </row>
     <row r="154" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B154" s="9">
@@ -5024,7 +4983,7 @@
       <c r="E154">
         <v>4.05</v>
       </c>
-      <c r="G154" s="33"/>
+      <c r="G154" s="29"/>
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B155" s="9">
@@ -5037,7 +4996,7 @@
       <c r="E155">
         <v>3.98</v>
       </c>
-      <c r="G155" s="33"/>
+      <c r="G155" s="29"/>
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B156" s="9">
@@ -5127,7 +5086,7 @@
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C4" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D4" s="8">
         <v>15520853.789999999</v>
@@ -5138,7 +5097,7 @@
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C5" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D5" s="8">
         <f>D4/12</f>
@@ -5151,7 +5110,7 @@
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C6" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D6" s="8">
         <v>8817263.6600000001</v>
@@ -5162,7 +5121,7 @@
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C7" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D7" s="8">
         <f>D6/7</f>
@@ -5296,7 +5255,7 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="26.25" x14ac:dyDescent="0.25">
@@ -5308,10 +5267,10 @@
       </c>
       <c r="E4" s="20"/>
       <c r="F4" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="G4" s="20" t="s">
         <v>336</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>337</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>266</v>
@@ -5326,19 +5285,19 @@
       <c r="C5" s="16">
         <v>275</v>
       </c>
-      <c r="E5" s="34" t="s">
-        <v>327</v>
-      </c>
-      <c r="F5" s="35">
+      <c r="E5" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="F5" s="34">
         <f>SUM(C5:C35)</f>
         <v>4138</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="34">
         <f>SUM(C5:C21)/72+C35/45</f>
         <v>61.322222222222223</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I5" s="7">
         <f>COUNTIF(C5:C15,"&lt;100")+COUNTIF(C20:C21,"&lt;100")</f>
@@ -5353,11 +5312,11 @@
       <c r="C6" s="16">
         <v>248</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I6" s="7">
         <f>COUNTIF(C5:C15,"&gt;300")+COUNTIF(C20:C21,"&gt;300")</f>
@@ -5373,7 +5332,7 @@
         <v>370</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F7" s="20">
         <v>0</v>
@@ -5393,7 +5352,7 @@
         <v>258</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F8" s="20">
         <f>SUM(C49:C56)</f>
@@ -5415,7 +5374,7 @@
         <v>283</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F9" s="22">
         <f>C62</f>
@@ -5436,26 +5395,26 @@
       <c r="C10" s="16">
         <v>318</v>
       </c>
-      <c r="E10" s="34" t="s">
-        <v>331</v>
-      </c>
-      <c r="F10" s="36">
+      <c r="E10" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="F10" s="35">
         <f>C81</f>
         <v>5160</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="36">
         <f>F10/42</f>
         <v>122.85714285714286</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I10" s="23">
         <f>39296/42/24</f>
         <v>38.984126984126981</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
@@ -5465,18 +5424,18 @@
       <c r="C11" s="16">
         <v>256</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="37"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="36"/>
       <c r="H11" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I11" s="7">
         <f>84672/42/24</f>
         <v>84</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
